--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_oil_gas_integrated.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09244428852554835</v>
+        <v>0.09224692780423446</v>
       </c>
       <c r="C2">
-        <v>1471.045926628064</v>
+        <v>1459.204044115038</v>
       </c>
       <c r="D2">
-        <v>1320.045926628064</v>
+        <v>1323.071044115038</v>
       </c>
       <c r="E2">
-        <v>-144</v>
+        <v>-129.133</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.867</v>
       </c>
       <c r="G2">
         <v>151</v>
@@ -1439,28 +1439,28 @@
         <v>163</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7478101</v>
       </c>
       <c r="N2">
-        <v>163</v>
+        <v>162.2521899</v>
       </c>
       <c r="O2">
-        <v>40.75</v>
+        <v>40.563047475</v>
       </c>
       <c r="P2">
-        <v>122.25</v>
+        <v>121.689142425</v>
       </c>
       <c r="Q2">
-        <v>188.25</v>
+        <v>187.689142425</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09244428852554835</v>
+        <v>0.09279765434771159</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9420050034730364</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>217.9697760166652</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09224692780423446</v>
+        <v>0.0920495670829206</v>
       </c>
       <c r="C3">
-        <v>1459.204044115038</v>
+        <v>1447.376058627398</v>
       </c>
       <c r="D3">
-        <v>1323.071044115038</v>
+        <v>1326.110058627398</v>
       </c>
       <c r="E3">
-        <v>-129.133</v>
+        <v>-114.266</v>
       </c>
       <c r="F3">
-        <v>14.867</v>
+        <v>29.734</v>
       </c>
       <c r="G3">
         <v>151</v>
@@ -1521,28 +1521,28 @@
         <v>163</v>
       </c>
       <c r="M3">
-        <v>0.7478101</v>
+        <v>1.4956202</v>
       </c>
       <c r="N3">
-        <v>162.2521899</v>
+        <v>161.5043798</v>
       </c>
       <c r="O3">
-        <v>40.563047475</v>
+        <v>40.37609495</v>
       </c>
       <c r="P3">
-        <v>121.689142425</v>
+        <v>121.12828485</v>
       </c>
       <c r="Q3">
-        <v>187.689142425</v>
+        <v>187.12828485</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09279765434771159</v>
+        <v>0.09315823171726592</v>
       </c>
       <c r="T3">
-        <v>0.9420050034730364</v>
+        <v>0.9492322936638684</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>217.9697760166652</v>
+        <v>108.9848880083326</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0920495670829206</v>
+        <v>0.09185220636160674</v>
       </c>
       <c r="C4">
-        <v>1447.376058627398</v>
+        <v>1435.562066147503</v>
       </c>
       <c r="D4">
-        <v>1326.110058627398</v>
+        <v>1329.163066147503</v>
       </c>
       <c r="E4">
-        <v>-114.266</v>
+        <v>-99.399</v>
       </c>
       <c r="F4">
-        <v>29.734</v>
+        <v>44.601</v>
       </c>
       <c r="G4">
         <v>151</v>
@@ -1603,28 +1603,28 @@
         <v>163</v>
       </c>
       <c r="M4">
-        <v>1.4956202</v>
+        <v>2.2434303</v>
       </c>
       <c r="N4">
-        <v>161.5043798</v>
+        <v>160.7565697</v>
       </c>
       <c r="O4">
-        <v>40.37609495</v>
+        <v>40.189142425</v>
       </c>
       <c r="P4">
-        <v>121.12828485</v>
+        <v>120.567427275</v>
       </c>
       <c r="Q4">
-        <v>187.12828485</v>
+        <v>186.567427275</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09315823171726592</v>
+        <v>0.09352624367175952</v>
       </c>
       <c r="T4">
-        <v>0.9492322936638684</v>
+        <v>0.9566086001472948</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>108.9848880083326</v>
+        <v>72.65659200555507</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09185220636160674</v>
+        <v>0.09165484564029287</v>
       </c>
       <c r="C5">
-        <v>1435.562066147503</v>
+        <v>1423.762163543641</v>
       </c>
       <c r="D5">
-        <v>1329.163066147503</v>
+        <v>1332.230163543641</v>
       </c>
       <c r="E5">
-        <v>-99.399</v>
+        <v>-84.532</v>
       </c>
       <c r="F5">
-        <v>44.601</v>
+        <v>59.468</v>
       </c>
       <c r="G5">
         <v>151</v>
@@ -1685,28 +1685,28 @@
         <v>163</v>
       </c>
       <c r="M5">
-        <v>2.2434303</v>
+        <v>2.9912404</v>
       </c>
       <c r="N5">
-        <v>160.7565697</v>
+        <v>160.0087596</v>
       </c>
       <c r="O5">
-        <v>40.189142425</v>
+        <v>40.0021899</v>
       </c>
       <c r="P5">
-        <v>120.567427275</v>
+        <v>120.0065697</v>
       </c>
       <c r="Q5">
-        <v>186.567427275</v>
+        <v>186.0065697</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09352624367175952</v>
+        <v>0.09390192254197174</v>
       </c>
       <c r="T5">
-        <v>0.9566086001472948</v>
+        <v>0.9641385796824593</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.65659200555507</v>
+        <v>54.49244400416629</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09165484564029287</v>
+        <v>0.091457484918979</v>
       </c>
       <c r="C6">
-        <v>1423.762163543641</v>
+        <v>1411.976448580281</v>
       </c>
       <c r="D6">
-        <v>1332.230163543641</v>
+        <v>1335.311448580281</v>
       </c>
       <c r="E6">
-        <v>-84.532</v>
+        <v>-69.66499999999999</v>
       </c>
       <c r="F6">
-        <v>59.468</v>
+        <v>74.33500000000001</v>
       </c>
       <c r="G6">
         <v>151</v>
@@ -1767,28 +1767,28 @@
         <v>163</v>
       </c>
       <c r="M6">
-        <v>2.9912404</v>
+        <v>3.7390505</v>
       </c>
       <c r="N6">
-        <v>160.0087596</v>
+        <v>159.2609495</v>
       </c>
       <c r="O6">
-        <v>40.0021899</v>
+        <v>39.815237375</v>
       </c>
       <c r="P6">
-        <v>120.0065697</v>
+        <v>119.445712125</v>
       </c>
       <c r="Q6">
-        <v>186.0065697</v>
+        <v>185.445712125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09390192254197174</v>
+        <v>0.09428551044103052</v>
       </c>
       <c r="T6">
-        <v>0.9641385796824593</v>
+        <v>0.9718270851025745</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.49244400416629</v>
+        <v>43.59395520333304</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.091457484918979</v>
+        <v>0.09126012419766513</v>
       </c>
       <c r="C7">
-        <v>1411.976448580281</v>
+        <v>1400.205019928454</v>
       </c>
       <c r="D7">
-        <v>1335.311448580281</v>
+        <v>1338.407019928454</v>
       </c>
       <c r="E7">
-        <v>-69.66499999999999</v>
+        <v>-54.79799999999999</v>
       </c>
       <c r="F7">
-        <v>74.33500000000001</v>
+        <v>89.20200000000001</v>
       </c>
       <c r="G7">
         <v>151</v>
@@ -1849,28 +1849,28 @@
         <v>163</v>
       </c>
       <c r="M7">
-        <v>3.7390505</v>
+        <v>4.4868606</v>
       </c>
       <c r="N7">
-        <v>159.2609495</v>
+        <v>158.5131394</v>
       </c>
       <c r="O7">
-        <v>39.815237375</v>
+        <v>39.62828485</v>
       </c>
       <c r="P7">
-        <v>119.445712125</v>
+        <v>118.88485455</v>
       </c>
       <c r="Q7">
-        <v>185.445712125</v>
+        <v>184.88485455</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09428551044103052</v>
+        <v>0.09467725978475014</v>
       </c>
       <c r="T7">
-        <v>0.9718270851025745</v>
+        <v>0.9796791757443944</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.59395520333304</v>
+        <v>36.32829600277753</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09126012419766513</v>
+        <v>0.09106276347635126</v>
       </c>
       <c r="C8">
-        <v>1400.205019928454</v>
+        <v>1388.447977176295</v>
       </c>
       <c r="D8">
-        <v>1338.407019928454</v>
+        <v>1341.516977176295</v>
       </c>
       <c r="E8">
-        <v>-54.798</v>
+        <v>-39.93100000000001</v>
       </c>
       <c r="F8">
-        <v>89.202</v>
+        <v>104.069</v>
       </c>
       <c r="G8">
         <v>151</v>
@@ -1931,28 +1931,28 @@
         <v>163</v>
       </c>
       <c r="M8">
-        <v>4.4868606</v>
+        <v>5.234670699999999</v>
       </c>
       <c r="N8">
-        <v>158.5131394</v>
+        <v>157.7653293</v>
       </c>
       <c r="O8">
-        <v>39.62828485</v>
+        <v>39.441332325</v>
       </c>
       <c r="P8">
-        <v>118.88485455</v>
+        <v>118.323996975</v>
       </c>
       <c r="Q8">
-        <v>184.88485455</v>
+        <v>184.323996975</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09467725978475014</v>
+        <v>0.09507743384553899</v>
       </c>
       <c r="T8">
-        <v>0.9796791757443944</v>
+        <v>0.9877001285505546</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.32829600277753</v>
+        <v>31.13853943095218</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09106276347635126</v>
+        <v>0.09086540275503738</v>
       </c>
       <c r="C9">
-        <v>1388.447977176295</v>
+        <v>1376.705420839711</v>
       </c>
       <c r="D9">
-        <v>1341.516977176295</v>
+        <v>1344.641420839711</v>
       </c>
       <c r="E9">
-        <v>-39.93099999999998</v>
+        <v>-25.06399999999999</v>
       </c>
       <c r="F9">
-        <v>104.069</v>
+        <v>118.936</v>
       </c>
       <c r="G9">
         <v>151</v>
@@ -2013,28 +2013,28 @@
         <v>163</v>
       </c>
       <c r="M9">
-        <v>5.234670700000001</v>
+        <v>5.9824808</v>
       </c>
       <c r="N9">
-        <v>157.7653293</v>
+        <v>157.0175192</v>
       </c>
       <c r="O9">
-        <v>39.441332325</v>
+        <v>39.2543798</v>
       </c>
       <c r="P9">
-        <v>118.323996975</v>
+        <v>117.7631394</v>
       </c>
       <c r="Q9">
-        <v>184.323996975</v>
+        <v>183.7631394</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09507743384553899</v>
+        <v>0.09548630734243194</v>
       </c>
       <c r="T9">
-        <v>0.9877001285505546</v>
+        <v>0.9958954498959791</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.13853943095216</v>
+        <v>27.24622200208315</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09086540275503738</v>
+        <v>0.09066804203372351</v>
       </c>
       <c r="C10">
-        <v>1376.705420839711</v>
+        <v>1364.977452373219</v>
       </c>
       <c r="D10">
-        <v>1344.641420839711</v>
+        <v>1347.780452373218</v>
       </c>
       <c r="E10">
-        <v>-25.06399999999999</v>
+        <v>-10.197</v>
       </c>
       <c r="F10">
-        <v>118.936</v>
+        <v>133.803</v>
       </c>
       <c r="G10">
         <v>151</v>
@@ -2095,28 +2095,28 @@
         <v>163</v>
       </c>
       <c r="M10">
-        <v>5.9824808</v>
+        <v>6.7302909</v>
       </c>
       <c r="N10">
-        <v>157.0175192</v>
+        <v>156.2697091</v>
       </c>
       <c r="O10">
-        <v>39.2543798</v>
+        <v>39.067427275</v>
       </c>
       <c r="P10">
-        <v>117.7631394</v>
+        <v>117.202281825</v>
       </c>
       <c r="Q10">
-        <v>183.7631394</v>
+        <v>183.202281825</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09548630734243194</v>
+        <v>0.09590416707002583</v>
       </c>
       <c r="T10">
-        <v>0.9958954498959791</v>
+        <v>1.00427088819405</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.24622200208315</v>
+        <v>24.21886400185169</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09066804203372351</v>
+        <v>0.09047068131240964</v>
       </c>
       <c r="C11">
-        <v>1364.977452373219</v>
+        <v>1353.264174180925</v>
       </c>
       <c r="D11">
-        <v>1347.780452373218</v>
+        <v>1350.934174180925</v>
       </c>
       <c r="E11">
-        <v>-10.197</v>
+        <v>4.669999999999987</v>
       </c>
       <c r="F11">
-        <v>133.803</v>
+        <v>148.67</v>
       </c>
       <c r="G11">
         <v>151</v>
@@ -2177,28 +2177,28 @@
         <v>163</v>
       </c>
       <c r="M11">
-        <v>6.7302909</v>
+        <v>7.478100999999999</v>
       </c>
       <c r="N11">
-        <v>156.2697091</v>
+        <v>155.521899</v>
       </c>
       <c r="O11">
-        <v>39.067427275</v>
+        <v>38.88047475</v>
       </c>
       <c r="P11">
-        <v>117.202281825</v>
+        <v>116.64142425</v>
       </c>
       <c r="Q11">
-        <v>183.202281825</v>
+        <v>182.64142425</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09590416707002583</v>
+        <v>0.09633131256934405</v>
       </c>
       <c r="T11">
-        <v>1.00427088819405</v>
+        <v>1.01283244734319</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.21886400185169</v>
+        <v>21.79697760166652</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09047068131240964</v>
+        <v>0.09027332059109577</v>
       </c>
       <c r="C12">
-        <v>1353.264174180925</v>
+        <v>1341.565689627661</v>
       </c>
       <c r="D12">
-        <v>1350.934174180925</v>
+        <v>1354.102689627661</v>
       </c>
       <c r="E12">
-        <v>4.670000000000016</v>
+        <v>19.53700000000001</v>
       </c>
       <c r="F12">
-        <v>148.67</v>
+        <v>163.537</v>
       </c>
       <c r="G12">
         <v>151</v>
@@ -2259,28 +2259,28 @@
         <v>163</v>
       </c>
       <c r="M12">
-        <v>7.478101000000001</v>
+        <v>8.225911099999999</v>
       </c>
       <c r="N12">
-        <v>155.521899</v>
+        <v>154.7740889</v>
       </c>
       <c r="O12">
-        <v>38.88047475</v>
+        <v>38.693522225</v>
       </c>
       <c r="P12">
-        <v>116.64142425</v>
+        <v>116.080566675</v>
       </c>
       <c r="Q12">
-        <v>182.64142425</v>
+        <v>182.080566675</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09633131256934405</v>
+        <v>0.09676805684392784</v>
       </c>
       <c r="T12">
-        <v>1.01283244734319</v>
+        <v>1.02158640107995</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.79697760166652</v>
+        <v>19.8154341833332</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09027332059109577</v>
+        <v>0.09007595986978191</v>
       </c>
       <c r="C13">
-        <v>1341.565689627661</v>
+        <v>1329.882103050274</v>
       </c>
       <c r="D13">
-        <v>1354.102689627661</v>
+        <v>1357.286103050274</v>
       </c>
       <c r="E13">
-        <v>19.53700000000001</v>
+        <v>34.404</v>
       </c>
       <c r="F13">
-        <v>163.537</v>
+        <v>178.404</v>
       </c>
       <c r="G13">
         <v>151</v>
@@ -2341,28 +2341,28 @@
         <v>163</v>
       </c>
       <c r="M13">
-        <v>8.225911099999999</v>
+        <v>8.9737212</v>
       </c>
       <c r="N13">
-        <v>154.7740889</v>
+        <v>154.0262788</v>
       </c>
       <c r="O13">
-        <v>38.693522225</v>
+        <v>38.5065697</v>
       </c>
       <c r="P13">
-        <v>116.080566675</v>
+        <v>115.5197091</v>
       </c>
       <c r="Q13">
-        <v>182.080566675</v>
+        <v>181.5197091</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09676805684392784</v>
+        <v>0.09721472712475217</v>
       </c>
       <c r="T13">
-        <v>1.02158640107995</v>
+        <v>1.030539308310728</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.8154341833332</v>
+        <v>18.16414800138877</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09007595986978191</v>
+        <v>0.08987859914846803</v>
       </c>
       <c r="C14">
-        <v>1329.882103050274</v>
+        <v>1318.213519769084</v>
       </c>
       <c r="D14">
-        <v>1357.286103050274</v>
+        <v>1360.484519769084</v>
       </c>
       <c r="E14">
-        <v>34.404</v>
+        <v>49.27100000000002</v>
       </c>
       <c r="F14">
-        <v>178.404</v>
+        <v>193.271</v>
       </c>
       <c r="G14">
         <v>151</v>
@@ -2423,28 +2423,28 @@
         <v>163</v>
       </c>
       <c r="M14">
-        <v>8.9737212</v>
+        <v>9.721531300000001</v>
       </c>
       <c r="N14">
-        <v>154.0262788</v>
+        <v>153.2784687</v>
       </c>
       <c r="O14">
-        <v>38.5065697</v>
+        <v>38.319617175</v>
       </c>
       <c r="P14">
-        <v>115.5197091</v>
+        <v>114.958851525</v>
       </c>
       <c r="Q14">
-        <v>181.5197091</v>
+        <v>180.958851525</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09721472712475217</v>
+        <v>0.09767166568789429</v>
       </c>
       <c r="T14">
-        <v>1.030539308310728</v>
+        <v>1.039698029500834</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.16414800138877</v>
+        <v>16.76690584743578</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08987859914846803</v>
+        <v>0.08968123842715414</v>
       </c>
       <c r="C15">
-        <v>1318.213519769084</v>
+        <v>1306.560046099495</v>
       </c>
       <c r="D15">
-        <v>1360.484519769084</v>
+        <v>1363.698046099495</v>
       </c>
       <c r="E15">
-        <v>49.27100000000002</v>
+        <v>64.13800000000003</v>
       </c>
       <c r="F15">
-        <v>193.271</v>
+        <v>208.138</v>
       </c>
       <c r="G15">
         <v>151</v>
@@ -2505,28 +2505,28 @@
         <v>163</v>
       </c>
       <c r="M15">
-        <v>9.721531300000001</v>
+        <v>10.4693414</v>
       </c>
       <c r="N15">
-        <v>153.2784687</v>
+        <v>152.5306586</v>
       </c>
       <c r="O15">
-        <v>38.319617175</v>
+        <v>38.13266465</v>
       </c>
       <c r="P15">
-        <v>114.958851525</v>
+        <v>114.39799395</v>
       </c>
       <c r="Q15">
-        <v>180.958851525</v>
+        <v>180.39799395</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09767166568789429</v>
+        <v>0.09813923072924902</v>
       </c>
       <c r="T15">
-        <v>1.039698029500834</v>
+        <v>1.049069744206989</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.76690584743578</v>
+        <v>15.56926971547608</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08968123842715414</v>
+        <v>0.08948387770584029</v>
       </c>
       <c r="C16">
-        <v>1306.560046099495</v>
+        <v>1294.921789363776</v>
       </c>
       <c r="D16">
-        <v>1363.698046099495</v>
+        <v>1366.926789363776</v>
       </c>
       <c r="E16">
-        <v>64.13800000000003</v>
+        <v>79.00500000000005</v>
       </c>
       <c r="F16">
-        <v>208.138</v>
+        <v>223.0050000000001</v>
       </c>
       <c r="G16">
         <v>151</v>
@@ -2587,28 +2587,28 @@
         <v>163</v>
       </c>
       <c r="M16">
-        <v>10.4693414</v>
+        <v>11.2171515</v>
       </c>
       <c r="N16">
-        <v>152.5306586</v>
+        <v>151.7828485</v>
       </c>
       <c r="O16">
-        <v>38.13266465</v>
+        <v>37.945712125</v>
       </c>
       <c r="P16">
-        <v>114.39799395</v>
+        <v>113.837136375</v>
       </c>
       <c r="Q16">
-        <v>180.39799395</v>
+        <v>179.837136375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09813923072924902</v>
+        <v>0.09861779730098857</v>
       </c>
       <c r="T16">
-        <v>1.049069744206989</v>
+        <v>1.058661969847406</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.56926971547608</v>
+        <v>14.53131840111101</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08948387770584029</v>
+        <v>0.08928651698452642</v>
       </c>
       <c r="C17">
-        <v>1294.921789363776</v>
+        <v>1283.298857903013</v>
       </c>
       <c r="D17">
-        <v>1366.926789363776</v>
+        <v>1370.170857903013</v>
       </c>
       <c r="E17">
-        <v>79.005</v>
+        <v>93.87200000000001</v>
       </c>
       <c r="F17">
-        <v>223.005</v>
+        <v>237.872</v>
       </c>
       <c r="G17">
         <v>151</v>
@@ -2669,28 +2669,28 @@
         <v>163</v>
       </c>
       <c r="M17">
-        <v>11.2171515</v>
+        <v>11.9649616</v>
       </c>
       <c r="N17">
-        <v>151.7828485</v>
+        <v>151.0350384</v>
       </c>
       <c r="O17">
-        <v>37.945712125</v>
+        <v>37.7587596</v>
       </c>
       <c r="P17">
-        <v>113.837136375</v>
+        <v>113.2762788</v>
       </c>
       <c r="Q17">
-        <v>179.837136375</v>
+        <v>179.2762788</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09861779730098857</v>
+        <v>0.09910775831491241</v>
       </c>
       <c r="T17">
-        <v>1.058661969847406</v>
+        <v>1.068482581812596</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.53131840111101</v>
+        <v>13.62311100104157</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08928651698452642</v>
+        <v>0.08928040626321254</v>
       </c>
       <c r="C18">
-        <v>1283.298857903013</v>
+        <v>1268.532547165574</v>
       </c>
       <c r="D18">
-        <v>1370.170857903013</v>
+        <v>1370.271547165574</v>
       </c>
       <c r="E18">
-        <v>93.87200000000001</v>
+        <v>108.739</v>
       </c>
       <c r="F18">
-        <v>237.872</v>
+        <v>252.739</v>
       </c>
       <c r="G18">
         <v>151</v>
@@ -2751,45 +2751,45 @@
         <v>163</v>
       </c>
       <c r="M18">
-        <v>11.9649616</v>
+        <v>13.0918802</v>
       </c>
       <c r="N18">
-        <v>151.0350384</v>
+        <v>149.9081198</v>
       </c>
       <c r="O18">
-        <v>37.7587596</v>
+        <v>37.47702995</v>
       </c>
       <c r="P18">
-        <v>113.2762788</v>
+        <v>112.43108985</v>
       </c>
       <c r="Q18">
-        <v>179.2762788</v>
+        <v>178.43108985</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09910775831491241</v>
+        <v>0.09960952561832837</v>
       </c>
       <c r="T18">
-        <v>1.068482581812596</v>
+        <v>1.078539835029958</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.62311100104157</v>
+        <v>12.4504652891645</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08928040626321254</v>
+        <v>0.08909429554189867</v>
       </c>
       <c r="C19">
-        <v>1268.532547165574</v>
+        <v>1256.739286889986</v>
       </c>
       <c r="D19">
-        <v>1370.271547165574</v>
+        <v>1373.345286889986</v>
       </c>
       <c r="E19">
-        <v>108.739</v>
+        <v>123.6060000000001</v>
       </c>
       <c r="F19">
-        <v>252.739</v>
+        <v>267.6060000000001</v>
       </c>
       <c r="G19">
         <v>151</v>
@@ -2833,28 +2833,28 @@
         <v>163</v>
       </c>
       <c r="M19">
-        <v>13.0918802</v>
+        <v>13.8619908</v>
       </c>
       <c r="N19">
-        <v>149.9081198</v>
+        <v>149.1380092</v>
       </c>
       <c r="O19">
-        <v>37.47702995</v>
+        <v>37.2845023</v>
       </c>
       <c r="P19">
-        <v>112.43108985</v>
+        <v>111.8535069</v>
       </c>
       <c r="Q19">
-        <v>178.43108985</v>
+        <v>177.8535069</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09960952561832837</v>
+        <v>0.1001235311486569</v>
       </c>
       <c r="T19">
-        <v>1.078539835029958</v>
+        <v>1.088842387106281</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.4504652891645</v>
+        <v>11.7587727730998</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08909429554189868</v>
+        <v>0.08890818482058481</v>
       </c>
       <c r="C20">
-        <v>1256.739286889985</v>
+        <v>1244.959847402935</v>
       </c>
       <c r="D20">
-        <v>1373.345286889985</v>
+        <v>1376.432847402935</v>
       </c>
       <c r="E20">
-        <v>123.606</v>
+        <v>138.473</v>
       </c>
       <c r="F20">
-        <v>267.606</v>
+        <v>282.473</v>
       </c>
       <c r="G20">
         <v>151</v>
@@ -2915,28 +2915,28 @@
         <v>163</v>
       </c>
       <c r="M20">
-        <v>13.8619908</v>
+        <v>14.6321014</v>
       </c>
       <c r="N20">
-        <v>149.1380092</v>
+        <v>148.3678986</v>
       </c>
       <c r="O20">
-        <v>37.2845023</v>
+        <v>37.09197465</v>
       </c>
       <c r="P20">
-        <v>111.8535069</v>
+        <v>111.27592395</v>
       </c>
       <c r="Q20">
-        <v>177.8535069</v>
+        <v>177.27592395</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1001235311486569</v>
+        <v>0.1006502281735615</v>
       </c>
       <c r="T20">
-        <v>1.088842387106281</v>
+        <v>1.099399323184488</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.75877277309981</v>
+        <v>11.13988999556824</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08890818482058481</v>
+        <v>0.08872207409927094</v>
       </c>
       <c r="C21">
-        <v>1244.959847402935</v>
+        <v>1233.194322130325</v>
       </c>
       <c r="D21">
-        <v>1376.432847402935</v>
+        <v>1379.534322130325</v>
       </c>
       <c r="E21">
-        <v>138.473</v>
+        <v>153.34</v>
       </c>
       <c r="F21">
-        <v>282.473</v>
+        <v>297.34</v>
       </c>
       <c r="G21">
         <v>151</v>
@@ -2997,28 +2997,28 @@
         <v>163</v>
       </c>
       <c r="M21">
-        <v>14.6321014</v>
+        <v>15.402212</v>
       </c>
       <c r="N21">
-        <v>148.3678986</v>
+        <v>147.597788</v>
       </c>
       <c r="O21">
-        <v>37.09197465</v>
+        <v>36.899447</v>
       </c>
       <c r="P21">
-        <v>111.27592395</v>
+        <v>110.698341</v>
       </c>
       <c r="Q21">
-        <v>177.27592395</v>
+        <v>176.698341</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1006502281735615</v>
+        <v>0.1011900926240887</v>
       </c>
       <c r="T21">
-        <v>1.099399323184488</v>
+        <v>1.11022018266465</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.13988999556824</v>
+        <v>10.58289549578983</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08872207409927094</v>
+        <v>0.08853596337795706</v>
       </c>
       <c r="C22">
-        <v>1233.194322130325</v>
+        <v>1221.442805342012</v>
       </c>
       <c r="D22">
-        <v>1379.534322130325</v>
+        <v>1382.649805342012</v>
       </c>
       <c r="E22">
-        <v>153.34</v>
+        <v>168.2070000000001</v>
       </c>
       <c r="F22">
-        <v>297.34</v>
+        <v>312.2070000000001</v>
       </c>
       <c r="G22">
         <v>151</v>
@@ -3079,28 +3079,28 @@
         <v>163</v>
       </c>
       <c r="M22">
-        <v>15.402212</v>
+        <v>16.1723226</v>
       </c>
       <c r="N22">
-        <v>147.597788</v>
+        <v>146.8276774</v>
       </c>
       <c r="O22">
-        <v>36.899447</v>
+        <v>36.70691935</v>
       </c>
       <c r="P22">
-        <v>110.698341</v>
+        <v>110.12075805</v>
       </c>
       <c r="Q22">
-        <v>176.698341</v>
+        <v>176.12075805</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1011900926240887</v>
+        <v>0.1017436245290596</v>
       </c>
       <c r="T22">
-        <v>1.11022018266465</v>
+        <v>1.121314987954437</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.58289549578983</v>
+        <v>10.0789480912284</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08853596337795706</v>
+        <v>0.08863035265664319</v>
       </c>
       <c r="C23">
-        <v>1221.442805342012</v>
+        <v>1204.99397742572</v>
       </c>
       <c r="D23">
-        <v>1382.649805342012</v>
+        <v>1381.06797742572</v>
       </c>
       <c r="E23">
-        <v>168.207</v>
+        <v>183.074</v>
       </c>
       <c r="F23">
-        <v>312.207</v>
+        <v>327.074</v>
       </c>
       <c r="G23">
         <v>151</v>
@@ -3161,45 +3161,45 @@
         <v>163</v>
       </c>
       <c r="M23">
-        <v>16.1723226</v>
+        <v>17.498459</v>
       </c>
       <c r="N23">
-        <v>146.8276774</v>
+        <v>145.501541</v>
       </c>
       <c r="O23">
-        <v>36.70691935</v>
+        <v>36.37538525</v>
       </c>
       <c r="P23">
-        <v>110.12075805</v>
+        <v>109.12615575</v>
       </c>
       <c r="Q23">
-        <v>176.12075805</v>
+        <v>175.12615575</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1017436245290596</v>
+        <v>0.102311349559799</v>
       </c>
       <c r="T23">
-        <v>1.121314987954437</v>
+        <v>1.132694275431141</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.07894809122841</v>
+        <v>9.315105975903364</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08863035265664319</v>
+        <v>0.08845699193532933</v>
       </c>
       <c r="C24">
-        <v>1204.99397742572</v>
+        <v>1193.035039337244</v>
       </c>
       <c r="D24">
-        <v>1381.06797742572</v>
+        <v>1383.976039337244</v>
       </c>
       <c r="E24">
-        <v>183.074</v>
+        <v>197.941</v>
       </c>
       <c r="F24">
-        <v>327.074</v>
+        <v>341.941</v>
       </c>
       <c r="G24">
         <v>151</v>
@@ -3243,28 +3243,28 @@
         <v>163</v>
       </c>
       <c r="M24">
-        <v>17.498459</v>
+        <v>18.2938435</v>
       </c>
       <c r="N24">
-        <v>145.501541</v>
+        <v>144.7061565</v>
       </c>
       <c r="O24">
-        <v>36.37538525</v>
+        <v>36.176539125</v>
       </c>
       <c r="P24">
-        <v>109.12615575</v>
+        <v>108.529617375</v>
       </c>
       <c r="Q24">
-        <v>175.12615575</v>
+        <v>174.529617375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.102311349559799</v>
+        <v>0.1028938206952329</v>
       </c>
       <c r="T24">
-        <v>1.132694275431141</v>
+        <v>1.144369128816331</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.315105975903364</v>
+        <v>8.91010136825539</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08845699193532933</v>
+        <v>0.08828363121401545</v>
       </c>
       <c r="C25">
-        <v>1193.035039337244</v>
+        <v>1181.088373879812</v>
       </c>
       <c r="D25">
-        <v>1383.976039337244</v>
+        <v>1386.896373879812</v>
       </c>
       <c r="E25">
-        <v>197.941</v>
+        <v>212.808</v>
       </c>
       <c r="F25">
-        <v>341.941</v>
+        <v>356.808</v>
       </c>
       <c r="G25">
         <v>151</v>
@@ -3325,28 +3325,28 @@
         <v>163</v>
       </c>
       <c r="M25">
-        <v>18.2938435</v>
+        <v>19.089228</v>
       </c>
       <c r="N25">
-        <v>144.7061565</v>
+        <v>143.910772</v>
       </c>
       <c r="O25">
-        <v>36.176539125</v>
+        <v>35.977693</v>
       </c>
       <c r="P25">
-        <v>108.529617375</v>
+        <v>107.933079</v>
       </c>
       <c r="Q25">
-        <v>174.529617375</v>
+        <v>173.933079</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1028938206952329</v>
+        <v>0.1034916200184414</v>
       </c>
       <c r="T25">
-        <v>1.144369128816331</v>
+        <v>1.156351215185342</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.91010136825539</v>
+        <v>8.538847144578083</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08828363121401545</v>
+        <v>0.08811027049270159</v>
       </c>
       <c r="C26">
-        <v>1181.088373879812</v>
+        <v>1169.154058907318</v>
       </c>
       <c r="D26">
-        <v>1386.896373879812</v>
+        <v>1389.829058907318</v>
       </c>
       <c r="E26">
-        <v>212.808</v>
+        <v>227.675</v>
       </c>
       <c r="F26">
-        <v>356.808</v>
+        <v>371.675</v>
       </c>
       <c r="G26">
         <v>151</v>
@@ -3407,28 +3407,28 @@
         <v>163</v>
       </c>
       <c r="M26">
-        <v>19.089228</v>
+        <v>19.8846125</v>
       </c>
       <c r="N26">
-        <v>143.910772</v>
+        <v>143.1153875</v>
       </c>
       <c r="O26">
-        <v>35.977693</v>
+        <v>35.778846875</v>
       </c>
       <c r="P26">
-        <v>107.933079</v>
+        <v>107.336540625</v>
       </c>
       <c r="Q26">
-        <v>173.933079</v>
+        <v>173.336540625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1034916200184414</v>
+        <v>0.1041053606569354</v>
       </c>
       <c r="T26">
-        <v>1.156351215185342</v>
+        <v>1.168652823857526</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.538847144578085</v>
+        <v>8.197293258794961</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08811027049270159</v>
+        <v>0.08793690977138771</v>
       </c>
       <c r="C27">
-        <v>1169.154058907318</v>
+        <v>1157.232172933562</v>
       </c>
       <c r="D27">
-        <v>1389.829058907318</v>
+        <v>1392.774172933562</v>
       </c>
       <c r="E27">
-        <v>227.675</v>
+        <v>242.542</v>
       </c>
       <c r="F27">
-        <v>371.675</v>
+        <v>386.542</v>
       </c>
       <c r="G27">
         <v>151</v>
@@ -3489,28 +3489,28 @@
         <v>163</v>
       </c>
       <c r="M27">
-        <v>19.8846125</v>
+        <v>20.679997</v>
       </c>
       <c r="N27">
-        <v>143.1153875</v>
+        <v>142.320003</v>
       </c>
       <c r="O27">
-        <v>35.778846875</v>
+        <v>35.58000075</v>
       </c>
       <c r="P27">
-        <v>107.336540625</v>
+        <v>106.74000225</v>
       </c>
       <c r="Q27">
-        <v>173.336540625</v>
+        <v>172.74000225</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1041053606569354</v>
+        <v>0.1047356888802537</v>
       </c>
       <c r="T27">
-        <v>1.168652823857526</v>
+        <v>1.18128690843977</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.197293258794961</v>
+        <v>7.882012748841307</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08793690977138771</v>
+        <v>0.08792554905007384</v>
       </c>
       <c r="C28">
-        <v>1157.232172933562</v>
+        <v>1142.558608774176</v>
       </c>
       <c r="D28">
-        <v>1392.774172933562</v>
+        <v>1392.967608774176</v>
       </c>
       <c r="E28">
-        <v>242.542</v>
+        <v>257.409</v>
       </c>
       <c r="F28">
-        <v>386.542</v>
+        <v>401.409</v>
       </c>
       <c r="G28">
         <v>151</v>
@@ -3571,45 +3571,45 @@
         <v>163</v>
       </c>
       <c r="M28">
-        <v>20.679997</v>
+        <v>21.7965087</v>
       </c>
       <c r="N28">
-        <v>142.320003</v>
+        <v>141.2034913</v>
       </c>
       <c r="O28">
-        <v>35.58000075</v>
+        <v>35.300872825</v>
       </c>
       <c r="P28">
-        <v>106.74000225</v>
+        <v>105.902618475</v>
       </c>
       <c r="Q28">
-        <v>172.74000225</v>
+        <v>171.902618475</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1047356888802537</v>
+        <v>0.1053832863699642</v>
       </c>
       <c r="T28">
-        <v>1.18128690843977</v>
+        <v>1.194267132325637</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.882012748841307</v>
+        <v>7.47826187411381</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08792554905007384</v>
+        <v>0.08775818832875996</v>
       </c>
       <c r="C29">
-        <v>1142.558608774176</v>
+        <v>1130.547452006487</v>
       </c>
       <c r="D29">
-        <v>1392.967608774176</v>
+        <v>1395.823452006487</v>
       </c>
       <c r="E29">
-        <v>257.409</v>
+        <v>272.2760000000001</v>
       </c>
       <c r="F29">
-        <v>401.409</v>
+        <v>416.2760000000001</v>
       </c>
       <c r="G29">
         <v>151</v>
@@ -3653,28 +3653,28 @@
         <v>163</v>
       </c>
       <c r="M29">
-        <v>21.7965087</v>
+        <v>22.60378680000001</v>
       </c>
       <c r="N29">
-        <v>141.2034913</v>
+        <v>140.3962132</v>
       </c>
       <c r="O29">
-        <v>35.300872825</v>
+        <v>35.0990533</v>
       </c>
       <c r="P29">
-        <v>105.902618475</v>
+        <v>105.2971599</v>
       </c>
       <c r="Q29">
-        <v>171.902618475</v>
+        <v>171.2971599</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1053832863699642</v>
+        <v>0.1060488726788333</v>
       </c>
       <c r="T29">
-        <v>1.194267132325637</v>
+        <v>1.207607917986111</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.47826187411381</v>
+        <v>7.21118109289546</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08775818832875996</v>
+        <v>0.0875908276074461</v>
       </c>
       <c r="C30">
-        <v>1130.547452006487</v>
+        <v>1118.548029317696</v>
       </c>
       <c r="D30">
-        <v>1395.823452006487</v>
+        <v>1398.691029317696</v>
       </c>
       <c r="E30">
-        <v>272.2760000000001</v>
+        <v>287.1430000000001</v>
       </c>
       <c r="F30">
-        <v>416.2760000000001</v>
+        <v>431.1430000000001</v>
       </c>
       <c r="G30">
         <v>151</v>
@@ -3735,28 +3735,28 @@
         <v>163</v>
       </c>
       <c r="M30">
-        <v>22.60378680000001</v>
+        <v>23.41106490000001</v>
       </c>
       <c r="N30">
-        <v>140.3962132</v>
+        <v>139.5889351</v>
       </c>
       <c r="O30">
-        <v>35.0990533</v>
+        <v>34.897233775</v>
       </c>
       <c r="P30">
-        <v>105.2971599</v>
+        <v>104.691701325</v>
       </c>
       <c r="Q30">
-        <v>171.2971599</v>
+        <v>170.691701325</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1060488726788333</v>
+        <v>0.1067332078978114</v>
       </c>
       <c r="T30">
-        <v>1.207607917986111</v>
+        <v>1.221324500425753</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.21118109289546</v>
+        <v>6.962519675899063</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08759082760744609</v>
+        <v>0.08742346688613223</v>
       </c>
       <c r="C31">
-        <v>1118.548029317696</v>
+        <v>1106.560413176098</v>
       </c>
       <c r="D31">
-        <v>1398.691029317696</v>
+        <v>1401.570413176098</v>
       </c>
       <c r="E31">
-        <v>287.143</v>
+        <v>302.01</v>
       </c>
       <c r="F31">
-        <v>431.143</v>
+        <v>446.01</v>
       </c>
       <c r="G31">
         <v>151</v>
@@ -3817,28 +3817,28 @@
         <v>163</v>
       </c>
       <c r="M31">
-        <v>23.4110649</v>
+        <v>24.218343</v>
       </c>
       <c r="N31">
-        <v>139.5889351</v>
+        <v>138.781657</v>
       </c>
       <c r="O31">
-        <v>34.897233775</v>
+        <v>34.69541425</v>
       </c>
       <c r="P31">
-        <v>104.691701325</v>
+        <v>104.08624275</v>
       </c>
       <c r="Q31">
-        <v>170.691701325</v>
+        <v>170.08624275</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1067332078978114</v>
+        <v>0.1074370955516175</v>
       </c>
       <c r="T31">
-        <v>1.221324500425753</v>
+        <v>1.235432985220814</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.962519675899067</v>
+        <v>6.73043568670243</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08742346688613223</v>
+        <v>0.08725610616481835</v>
       </c>
       <c r="C32">
-        <v>1106.560413176098</v>
+        <v>1094.584676647958</v>
       </c>
       <c r="D32">
-        <v>1401.570413176098</v>
+        <v>1404.461676647958</v>
       </c>
       <c r="E32">
-        <v>302.01</v>
+        <v>316.877</v>
       </c>
       <c r="F32">
-        <v>446.01</v>
+        <v>460.877</v>
       </c>
       <c r="G32">
         <v>151</v>
@@ -3899,28 +3899,28 @@
         <v>163</v>
       </c>
       <c r="M32">
-        <v>24.218343</v>
+        <v>25.0256211</v>
       </c>
       <c r="N32">
-        <v>138.781657</v>
+        <v>137.9743789</v>
       </c>
       <c r="O32">
-        <v>34.69541425</v>
+        <v>34.493594725</v>
       </c>
       <c r="P32">
-        <v>104.08624275</v>
+        <v>103.480784175</v>
       </c>
       <c r="Q32">
-        <v>170.08624275</v>
+        <v>169.480784175</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1074370955516175</v>
+        <v>0.1081613857461136</v>
       </c>
       <c r="T32">
-        <v>1.235432985220814</v>
+        <v>1.249950411604137</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.73043568670243</v>
+        <v>6.513324858099126</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08725610616481835</v>
+        <v>0.08708874544350448</v>
       </c>
       <c r="C33">
-        <v>1094.584676647958</v>
+        <v>1082.620893403694</v>
       </c>
       <c r="D33">
-        <v>1404.461676647958</v>
+        <v>1407.364893403694</v>
       </c>
       <c r="E33">
-        <v>316.877</v>
+        <v>331.744</v>
       </c>
       <c r="F33">
-        <v>460.877</v>
+        <v>475.744</v>
       </c>
       <c r="G33">
         <v>151</v>
@@ -3981,28 +3981,28 @@
         <v>163</v>
       </c>
       <c r="M33">
-        <v>25.0256211</v>
+        <v>25.8328992</v>
       </c>
       <c r="N33">
-        <v>137.9743789</v>
+        <v>137.1671008</v>
       </c>
       <c r="O33">
-        <v>34.493594725</v>
+        <v>34.2917752</v>
       </c>
       <c r="P33">
-        <v>103.480784175</v>
+        <v>102.8753256</v>
       </c>
       <c r="Q33">
-        <v>169.480784175</v>
+        <v>168.8753256</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1081613857461136</v>
+        <v>0.1089069785933889</v>
       </c>
       <c r="T33">
-        <v>1.249950411604137</v>
+        <v>1.264894821116382</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.513324858099126</v>
+        <v>6.309783456283527</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08708874544350448</v>
+        <v>0.08692138472219062</v>
       </c>
       <c r="C34">
-        <v>1082.620893403694</v>
+        <v>1070.669137724132</v>
       </c>
       <c r="D34">
-        <v>1407.364893403694</v>
+        <v>1410.280137724133</v>
       </c>
       <c r="E34">
-        <v>331.744</v>
+        <v>346.611</v>
       </c>
       <c r="F34">
-        <v>475.744</v>
+        <v>490.611</v>
       </c>
       <c r="G34">
         <v>151</v>
@@ -4063,28 +4063,28 @@
         <v>163</v>
       </c>
       <c r="M34">
-        <v>25.8328992</v>
+        <v>26.6401773</v>
       </c>
       <c r="N34">
-        <v>137.1671008</v>
+        <v>136.3598227</v>
       </c>
       <c r="O34">
-        <v>34.2917752</v>
+        <v>34.089955675</v>
       </c>
       <c r="P34">
-        <v>102.8753256</v>
+        <v>102.269867025</v>
       </c>
       <c r="Q34">
-        <v>168.8753256</v>
+        <v>168.269867025</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1089069785933889</v>
+        <v>0.1096748279435681</v>
       </c>
       <c r="T34">
-        <v>1.264894821116382</v>
+        <v>1.280285332405111</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.309783456283527</v>
+        <v>6.118577897002209</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08692138472219062</v>
+        <v>0.08700902400087673</v>
       </c>
       <c r="C35">
-        <v>1070.669137724132</v>
+        <v>1054.274050793619</v>
       </c>
       <c r="D35">
-        <v>1410.280137724133</v>
+        <v>1408.752050793619</v>
       </c>
       <c r="E35">
-        <v>346.611</v>
+        <v>361.4780000000001</v>
       </c>
       <c r="F35">
-        <v>490.611</v>
+        <v>505.4780000000001</v>
       </c>
       <c r="G35">
         <v>151</v>
@@ -4145,45 +4145,45 @@
         <v>163</v>
       </c>
       <c r="M35">
-        <v>26.6401773</v>
+        <v>27.95293340000001</v>
       </c>
       <c r="N35">
-        <v>136.3598227</v>
+        <v>135.0470666</v>
       </c>
       <c r="O35">
-        <v>34.089955675</v>
+        <v>33.76176665</v>
       </c>
       <c r="P35">
-        <v>102.269867025</v>
+        <v>101.28529995</v>
       </c>
       <c r="Q35">
-        <v>168.269867025</v>
+        <v>167.28529995</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1096748279435681</v>
+        <v>0.1104659454558738</v>
       </c>
       <c r="T35">
-        <v>1.280285332405111</v>
+        <v>1.296142222823802</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.118577897002209</v>
+        <v>5.831230578469448</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08700902400087673</v>
+        <v>0.08684916327956285</v>
       </c>
       <c r="C36">
-        <v>1054.274050793619</v>
+        <v>1042.196891567839</v>
       </c>
       <c r="D36">
-        <v>1408.752050793619</v>
+        <v>1411.541891567839</v>
       </c>
       <c r="E36">
-        <v>361.4780000000001</v>
+        <v>376.345</v>
       </c>
       <c r="F36">
-        <v>505.4780000000001</v>
+        <v>520.345</v>
       </c>
       <c r="G36">
         <v>151</v>
@@ -4227,28 +4227,28 @@
         <v>163</v>
       </c>
       <c r="M36">
-        <v>27.95293340000001</v>
+        <v>28.7750785</v>
       </c>
       <c r="N36">
-        <v>135.0470666</v>
+        <v>134.2249215</v>
       </c>
       <c r="O36">
-        <v>33.76176665</v>
+        <v>33.556230375</v>
       </c>
       <c r="P36">
-        <v>101.28529995</v>
+        <v>100.668691125</v>
       </c>
       <c r="Q36">
-        <v>167.28529995</v>
+        <v>166.668691125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1104659454558738</v>
+        <v>0.1112814050454813</v>
       </c>
       <c r="T36">
-        <v>1.296142222823802</v>
+        <v>1.312487017563068</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.831230578469448</v>
+        <v>5.664623990513179</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08684916327956285</v>
+        <v>0.086689302558249</v>
       </c>
       <c r="C37">
-        <v>1042.196891567839</v>
+        <v>1030.130804064314</v>
       </c>
       <c r="D37">
-        <v>1411.541891567839</v>
+        <v>1414.342804064315</v>
       </c>
       <c r="E37">
-        <v>376.345</v>
+        <v>391.2120000000001</v>
       </c>
       <c r="F37">
-        <v>520.345</v>
+        <v>535.2120000000001</v>
       </c>
       <c r="G37">
         <v>151</v>
@@ -4309,28 +4309,28 @@
         <v>163</v>
       </c>
       <c r="M37">
-        <v>28.7750785</v>
+        <v>29.59722360000001</v>
       </c>
       <c r="N37">
-        <v>134.2249215</v>
+        <v>133.4027764</v>
       </c>
       <c r="O37">
-        <v>33.556230375</v>
+        <v>33.3506941</v>
       </c>
       <c r="P37">
-        <v>100.668691125</v>
+        <v>100.0520823</v>
       </c>
       <c r="Q37">
-        <v>166.668691125</v>
+        <v>166.0520823</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1112814050454813</v>
+        <v>0.1121223477472641</v>
       </c>
       <c r="T37">
-        <v>1.312487017563068</v>
+        <v>1.329342587137936</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.664623990513179</v>
+        <v>5.507273324110034</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.086689302558249</v>
+        <v>0.08652944183693512</v>
       </c>
       <c r="C38">
-        <v>1030.130804064315</v>
+        <v>1018.075854322706</v>
       </c>
       <c r="D38">
-        <v>1414.342804064315</v>
+        <v>1417.154854322706</v>
       </c>
       <c r="E38">
-        <v>391.212</v>
+        <v>406.0790000000001</v>
       </c>
       <c r="F38">
-        <v>535.212</v>
+        <v>550.0790000000001</v>
       </c>
       <c r="G38">
         <v>151</v>
@@ -4391,28 +4391,28 @@
         <v>163</v>
       </c>
       <c r="M38">
-        <v>29.5972236</v>
+        <v>30.4193687</v>
       </c>
       <c r="N38">
-        <v>133.4027764</v>
+        <v>132.5806313</v>
       </c>
       <c r="O38">
-        <v>33.3506941</v>
+        <v>33.145157825</v>
       </c>
       <c r="P38">
-        <v>100.0520823</v>
+        <v>99.43547347499999</v>
       </c>
       <c r="Q38">
-        <v>166.0520823</v>
+        <v>165.435473475</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1121223477472641</v>
+        <v>0.1129899870427542</v>
       </c>
       <c r="T38">
-        <v>1.329342587137936</v>
+        <v>1.346733254159626</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.507273324110035</v>
+        <v>5.358428099134088</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08652944183693512</v>
+        <v>0.08636958111562125</v>
       </c>
       <c r="C39">
-        <v>1018.075854322706</v>
+        <v>1006.03210890893</v>
       </c>
       <c r="D39">
-        <v>1417.154854322706</v>
+        <v>1419.97810890893</v>
       </c>
       <c r="E39">
-        <v>406.0790000000001</v>
+        <v>420.946</v>
       </c>
       <c r="F39">
-        <v>550.0790000000001</v>
+        <v>564.946</v>
       </c>
       <c r="G39">
         <v>151</v>
@@ -4473,28 +4473,28 @@
         <v>163</v>
       </c>
       <c r="M39">
-        <v>30.4193687</v>
+        <v>31.2415138</v>
       </c>
       <c r="N39">
-        <v>132.5806313</v>
+        <v>131.7584862</v>
       </c>
       <c r="O39">
-        <v>33.145157825</v>
+        <v>32.93962155</v>
       </c>
       <c r="P39">
-        <v>99.43547347499999</v>
+        <v>98.81886464999999</v>
       </c>
       <c r="Q39">
-        <v>165.435473475</v>
+        <v>164.81886465</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1129899870427542</v>
+        <v>0.1138856147026149</v>
       </c>
       <c r="T39">
-        <v>1.346733254159626</v>
+        <v>1.364684910440079</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.358428099134088</v>
+        <v>5.217416833367402</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08636958111562125</v>
+        <v>0.0862097203943074</v>
       </c>
       <c r="C40">
-        <v>1006.03210890893</v>
+        <v>993.9996349204117</v>
       </c>
       <c r="D40">
-        <v>1419.97810890893</v>
+        <v>1422.812634920412</v>
       </c>
       <c r="E40">
-        <v>420.946</v>
+        <v>435.813</v>
       </c>
       <c r="F40">
-        <v>564.946</v>
+        <v>579.813</v>
       </c>
       <c r="G40">
         <v>151</v>
@@ -4555,28 +4555,28 @@
         <v>163</v>
       </c>
       <c r="M40">
-        <v>31.2415138</v>
+        <v>32.0636589</v>
       </c>
       <c r="N40">
-        <v>131.7584862</v>
+        <v>130.9363411</v>
       </c>
       <c r="O40">
-        <v>32.93962155</v>
+        <v>32.734085275</v>
       </c>
       <c r="P40">
-        <v>98.81886464999999</v>
+        <v>98.20225582499999</v>
       </c>
       <c r="Q40">
-        <v>164.81886465</v>
+        <v>164.202255825</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1138856147026149</v>
+        <v>0.1148106072037826</v>
       </c>
       <c r="T40">
-        <v>1.364684910440079</v>
+        <v>1.383225145614974</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.217416833367402</v>
+        <v>5.08363691456311</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0862097203943074</v>
+        <v>0.0860498596729935</v>
       </c>
       <c r="C41">
-        <v>993.9996349204117</v>
+        <v>981.9784999914036</v>
       </c>
       <c r="D41">
-        <v>1422.812634920412</v>
+        <v>1425.658499991404</v>
       </c>
       <c r="E41">
-        <v>435.813</v>
+        <v>450.6800000000001</v>
       </c>
       <c r="F41">
-        <v>579.813</v>
+        <v>594.6800000000001</v>
       </c>
       <c r="G41">
         <v>151</v>
@@ -4637,28 +4637,28 @@
         <v>163</v>
       </c>
       <c r="M41">
-        <v>32.0636589</v>
+        <v>32.88580400000001</v>
       </c>
       <c r="N41">
-        <v>130.9363411</v>
+        <v>130.114196</v>
       </c>
       <c r="O41">
-        <v>32.734085275</v>
+        <v>32.528549</v>
       </c>
       <c r="P41">
-        <v>98.20225582499999</v>
+        <v>97.58564699999999</v>
       </c>
       <c r="Q41">
-        <v>164.202255825</v>
+        <v>163.585647</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1148106072037826</v>
+        <v>0.1157664327883225</v>
       </c>
       <c r="T41">
-        <v>1.383225145614974</v>
+        <v>1.402383388629032</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.08363691456311</v>
+        <v>4.956545991699031</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0860498596729935</v>
+        <v>0.08588999895167965</v>
       </c>
       <c r="C42">
-        <v>981.9784999914036</v>
+        <v>969.9687722983588</v>
       </c>
       <c r="D42">
-        <v>1425.658499991404</v>
+        <v>1428.515772298359</v>
       </c>
       <c r="E42">
-        <v>450.6800000000001</v>
+        <v>465.547</v>
       </c>
       <c r="F42">
-        <v>594.6800000000001</v>
+        <v>609.547</v>
       </c>
       <c r="G42">
         <v>151</v>
@@ -4719,28 +4719,28 @@
         <v>163</v>
       </c>
       <c r="M42">
-        <v>32.88580400000001</v>
+        <v>33.7079491</v>
       </c>
       <c r="N42">
-        <v>130.114196</v>
+        <v>129.2920509</v>
       </c>
       <c r="O42">
-        <v>32.528549</v>
+        <v>32.323012725</v>
       </c>
       <c r="P42">
-        <v>97.58564699999999</v>
+        <v>96.96903817499999</v>
       </c>
       <c r="Q42">
-        <v>163.585647</v>
+        <v>162.969038175</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1157664327883225</v>
+        <v>0.116754659240135</v>
       </c>
       <c r="T42">
-        <v>1.402383388629032</v>
+        <v>1.422191063609668</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.956545991699031</v>
+        <v>4.835654626047836</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08588999895167965</v>
+        <v>0.08573013823036577</v>
       </c>
       <c r="C43">
-        <v>969.9687722983588</v>
+        <v>957.9705205653812</v>
       </c>
       <c r="D43">
-        <v>1428.515772298359</v>
+        <v>1431.384520565381</v>
       </c>
       <c r="E43">
-        <v>465.547</v>
+        <v>480.4140000000001</v>
       </c>
       <c r="F43">
-        <v>609.547</v>
+        <v>624.4140000000001</v>
       </c>
       <c r="G43">
         <v>151</v>
@@ -4801,28 +4801,28 @@
         <v>163</v>
       </c>
       <c r="M43">
-        <v>33.7079491</v>
+        <v>34.53009420000001</v>
       </c>
       <c r="N43">
-        <v>129.2920509</v>
+        <v>128.4699058</v>
       </c>
       <c r="O43">
-        <v>32.323012725</v>
+        <v>32.11747645</v>
       </c>
       <c r="P43">
-        <v>96.96903817499999</v>
+        <v>96.35242934999999</v>
       </c>
       <c r="Q43">
-        <v>162.969038175</v>
+        <v>162.35242935</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.116754659240135</v>
+        <v>0.1177769624661479</v>
       </c>
       <c r="T43">
-        <v>1.422191063609668</v>
+        <v>1.442681761865498</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.835654626047836</v>
+        <v>4.720519992094315</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08573013823036577</v>
+        <v>0.08557027750905191</v>
       </c>
       <c r="C44">
-        <v>957.9705205653813</v>
+        <v>945.9838140697319</v>
       </c>
       <c r="D44">
-        <v>1431.384520565381</v>
+        <v>1434.264814069732</v>
       </c>
       <c r="E44">
-        <v>480.414</v>
+        <v>495.2810000000001</v>
       </c>
       <c r="F44">
-        <v>624.414</v>
+        <v>639.2810000000001</v>
       </c>
       <c r="G44">
         <v>151</v>
@@ -4883,28 +4883,28 @@
         <v>163</v>
       </c>
       <c r="M44">
-        <v>34.5300942</v>
+        <v>35.35223930000001</v>
       </c>
       <c r="N44">
-        <v>128.4699058</v>
+        <v>127.6477607</v>
       </c>
       <c r="O44">
-        <v>32.11747645</v>
+        <v>31.911940175</v>
       </c>
       <c r="P44">
-        <v>96.35242934999999</v>
+        <v>95.73582052499999</v>
       </c>
       <c r="Q44">
-        <v>162.35242935</v>
+        <v>161.735820525</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1177769624661479</v>
+        <v>0.1188351359807928</v>
       </c>
       <c r="T44">
-        <v>1.442681761865498</v>
+        <v>1.463891431989954</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.720519992094315</v>
+        <v>4.610740457394447</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08557027750905191</v>
+        <v>0.08541041678773804</v>
       </c>
       <c r="C45">
-        <v>945.9838140697319</v>
+        <v>934.008722647408</v>
       </c>
       <c r="D45">
-        <v>1434.264814069732</v>
+        <v>1437.156722647408</v>
       </c>
       <c r="E45">
-        <v>495.2810000000001</v>
+        <v>510.148</v>
       </c>
       <c r="F45">
-        <v>639.2810000000001</v>
+        <v>654.148</v>
       </c>
       <c r="G45">
         <v>151</v>
@@ -4965,28 +4965,28 @@
         <v>163</v>
       </c>
       <c r="M45">
-        <v>35.35223930000001</v>
+        <v>36.1743844</v>
       </c>
       <c r="N45">
-        <v>127.6477607</v>
+        <v>126.8256156</v>
       </c>
       <c r="O45">
-        <v>31.911940175</v>
+        <v>31.7064039</v>
       </c>
       <c r="P45">
-        <v>95.73582052499999</v>
+        <v>95.11921169999999</v>
       </c>
       <c r="Q45">
-        <v>161.735820525</v>
+        <v>161.1192117</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1188351359807928</v>
+        <v>0.1199311014066751</v>
       </c>
       <c r="T45">
-        <v>1.463891431989954</v>
+        <v>1.485858590333141</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.610740457394447</v>
+        <v>4.505950901544574</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08541041678773804</v>
+        <v>0.08609430606642415</v>
       </c>
       <c r="C46">
-        <v>934.008722647408</v>
+        <v>906.8511165175938</v>
       </c>
       <c r="D46">
-        <v>1437.156722647408</v>
+        <v>1424.866116517594</v>
       </c>
       <c r="E46">
-        <v>510.148</v>
+        <v>525.015</v>
       </c>
       <c r="F46">
-        <v>654.148</v>
+        <v>669.015</v>
       </c>
       <c r="G46">
         <v>151</v>
@@ -5047,45 +5047,45 @@
         <v>163</v>
       </c>
       <c r="M46">
-        <v>36.1743844</v>
+        <v>38.66906700000001</v>
       </c>
       <c r="N46">
-        <v>126.8256156</v>
+        <v>124.330933</v>
       </c>
       <c r="O46">
-        <v>31.7064039</v>
+        <v>31.08273325</v>
       </c>
       <c r="P46">
-        <v>95.11921169999999</v>
+        <v>93.24819975</v>
       </c>
       <c r="Q46">
-        <v>161.1192117</v>
+        <v>159.24819975</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1199311014066751</v>
+        <v>0.1210669201207712</v>
       </c>
       <c r="T46">
-        <v>1.485858590333141</v>
+        <v>1.508624554434261</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.505950901544574</v>
+        <v>4.215255568488373</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08609430606642415</v>
+        <v>0.08595319534511028</v>
       </c>
       <c r="C47">
-        <v>906.8511165175938</v>
+        <v>894.5028630985071</v>
       </c>
       <c r="D47">
-        <v>1424.866116517594</v>
+        <v>1427.384863098507</v>
       </c>
       <c r="E47">
-        <v>525.015</v>
+        <v>539.8820000000001</v>
       </c>
       <c r="F47">
-        <v>669.015</v>
+        <v>683.8820000000001</v>
       </c>
       <c r="G47">
         <v>151</v>
@@ -5129,28 +5129,28 @@
         <v>163</v>
       </c>
       <c r="M47">
-        <v>38.66906700000001</v>
+        <v>39.52837960000001</v>
       </c>
       <c r="N47">
-        <v>124.330933</v>
+        <v>123.4716204</v>
       </c>
       <c r="O47">
-        <v>31.08273325</v>
+        <v>30.8679051</v>
       </c>
       <c r="P47">
-        <v>93.24819975</v>
+        <v>92.60371529999999</v>
       </c>
       <c r="Q47">
-        <v>159.24819975</v>
+        <v>158.6037153</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1210669201207712</v>
+        <v>0.1222448061946487</v>
       </c>
       <c r="T47">
-        <v>1.508624554434261</v>
+        <v>1.532233702390979</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.215255568488373</v>
+        <v>4.123619577869061</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08595319534511028</v>
+        <v>0.08581208462379643</v>
       </c>
       <c r="C48">
-        <v>894.5028630985071</v>
+        <v>882.1635302630593</v>
       </c>
       <c r="D48">
-        <v>1427.384863098507</v>
+        <v>1429.912530263059</v>
       </c>
       <c r="E48">
-        <v>539.8820000000001</v>
+        <v>554.749</v>
       </c>
       <c r="F48">
-        <v>683.8820000000001</v>
+        <v>698.749</v>
       </c>
       <c r="G48">
         <v>151</v>
@@ -5211,28 +5211,28 @@
         <v>163</v>
       </c>
       <c r="M48">
-        <v>39.52837960000001</v>
+        <v>40.3876922</v>
       </c>
       <c r="N48">
-        <v>123.4716204</v>
+        <v>122.6123078</v>
       </c>
       <c r="O48">
-        <v>30.8679051</v>
+        <v>30.65307695</v>
       </c>
       <c r="P48">
-        <v>92.60371529999999</v>
+        <v>91.95923085</v>
       </c>
       <c r="Q48">
-        <v>158.6037153</v>
+        <v>157.95923085</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1222448061946487</v>
+        <v>0.1234671407996159</v>
       </c>
       <c r="T48">
-        <v>1.532233702390979</v>
+        <v>1.556733761591346</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.123619577869061</v>
+        <v>4.035882991105889</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08581208462379643</v>
+        <v>0.08693097390248256</v>
       </c>
       <c r="C49">
-        <v>882.1635302630593</v>
+        <v>847.4967783520132</v>
       </c>
       <c r="D49">
-        <v>1429.912530263059</v>
+        <v>1410.112778352013</v>
       </c>
       <c r="E49">
-        <v>554.749</v>
+        <v>569.6160000000001</v>
       </c>
       <c r="F49">
-        <v>698.749</v>
+        <v>713.6160000000001</v>
       </c>
       <c r="G49">
         <v>151</v>
@@ -5293,45 +5293,45 @@
         <v>163</v>
       </c>
       <c r="M49">
-        <v>40.3876922</v>
+        <v>43.74466080000001</v>
       </c>
       <c r="N49">
-        <v>122.6123078</v>
+        <v>119.2553392</v>
       </c>
       <c r="O49">
-        <v>30.65307695</v>
+        <v>29.8138348</v>
       </c>
       <c r="P49">
-        <v>91.95923085</v>
+        <v>89.4415044</v>
       </c>
       <c r="Q49">
-        <v>157.95923085</v>
+        <v>155.4415044</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1234671407996159</v>
+        <v>0.1247364882740049</v>
       </c>
       <c r="T49">
-        <v>1.556733761591346</v>
+        <v>1.582176130760959</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.035882991105889</v>
+        <v>3.726169023123388</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08693097390248256</v>
+        <v>0.08681611318116868</v>
       </c>
       <c r="C50">
-        <v>847.4967783520133</v>
+        <v>834.6370507990381</v>
       </c>
       <c r="D50">
-        <v>1410.112778352013</v>
+        <v>1412.120050799038</v>
       </c>
       <c r="E50">
-        <v>569.616</v>
+        <v>584.4830000000001</v>
       </c>
       <c r="F50">
-        <v>713.616</v>
+        <v>728.4830000000001</v>
       </c>
       <c r="G50">
         <v>151</v>
@@ -5375,28 +5375,28 @@
         <v>163</v>
       </c>
       <c r="M50">
-        <v>43.7446608</v>
+        <v>44.65600790000001</v>
       </c>
       <c r="N50">
-        <v>119.2553392</v>
+        <v>118.3439921</v>
       </c>
       <c r="O50">
-        <v>29.8138348</v>
+        <v>29.585998025</v>
       </c>
       <c r="P50">
-        <v>89.44150440000001</v>
+        <v>88.757994075</v>
       </c>
       <c r="Q50">
-        <v>155.4415044</v>
+        <v>154.757994075</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1247364882740049</v>
+        <v>0.1260556140807229</v>
       </c>
       <c r="T50">
-        <v>1.582176130760959</v>
+        <v>1.608616239898007</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.726169023123389</v>
+        <v>3.65012475734536</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08681611318116868</v>
+        <v>0.0867012524598548</v>
       </c>
       <c r="C51">
-        <v>834.6370507990381</v>
+        <v>821.7830460312658</v>
       </c>
       <c r="D51">
-        <v>1412.120050799038</v>
+        <v>1414.133046031266</v>
       </c>
       <c r="E51">
-        <v>584.4830000000001</v>
+        <v>599.35</v>
       </c>
       <c r="F51">
-        <v>728.4830000000001</v>
+        <v>743.35</v>
       </c>
       <c r="G51">
         <v>151</v>
@@ -5457,28 +5457,28 @@
         <v>163</v>
       </c>
       <c r="M51">
-        <v>44.65600790000001</v>
+        <v>45.567355</v>
       </c>
       <c r="N51">
-        <v>118.3439921</v>
+        <v>117.432645</v>
       </c>
       <c r="O51">
-        <v>29.585998025</v>
+        <v>29.35816125</v>
       </c>
       <c r="P51">
-        <v>88.757994075</v>
+        <v>88.07448375000001</v>
       </c>
       <c r="Q51">
-        <v>154.757994075</v>
+        <v>154.07448375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1260556140807229</v>
+        <v>0.1274275049197096</v>
       </c>
       <c r="T51">
-        <v>1.608616239898007</v>
+        <v>1.636113953400537</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.65012475734536</v>
+        <v>3.577122262198453</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0867012524598548</v>
+        <v>0.08658639173854094</v>
       </c>
       <c r="C52">
-        <v>821.7830460312658</v>
+        <v>808.9347885573444</v>
       </c>
       <c r="D52">
-        <v>1414.133046031266</v>
+        <v>1416.151788557344</v>
       </c>
       <c r="E52">
-        <v>599.35</v>
+        <v>614.217</v>
       </c>
       <c r="F52">
-        <v>743.35</v>
+        <v>758.217</v>
       </c>
       <c r="G52">
         <v>151</v>
@@ -5539,28 +5539,28 @@
         <v>163</v>
       </c>
       <c r="M52">
-        <v>45.567355</v>
+        <v>46.4787021</v>
       </c>
       <c r="N52">
-        <v>117.432645</v>
+        <v>116.5212979</v>
       </c>
       <c r="O52">
-        <v>29.35816125</v>
+        <v>29.130324475</v>
       </c>
       <c r="P52">
-        <v>88.07448375000001</v>
+        <v>87.390973425</v>
       </c>
       <c r="Q52">
-        <v>154.07448375</v>
+        <v>153.390973425</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1274275049197096</v>
+        <v>0.1288553913031448</v>
       </c>
       <c r="T52">
-        <v>1.636113953400537</v>
+        <v>1.664734022556232</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.577122262198453</v>
+        <v>3.506982609998484</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08658639173854094</v>
+        <v>0.08756353101722707</v>
       </c>
       <c r="C53">
-        <v>808.9347885573444</v>
+        <v>777.0758500835757</v>
       </c>
       <c r="D53">
-        <v>1416.151788557344</v>
+        <v>1399.159850083576</v>
       </c>
       <c r="E53">
-        <v>614.217</v>
+        <v>629.0840000000001</v>
       </c>
       <c r="F53">
-        <v>758.217</v>
+        <v>773.0840000000001</v>
       </c>
       <c r="G53">
         <v>151</v>
@@ -5621,45 +5621,45 @@
         <v>163</v>
       </c>
       <c r="M53">
-        <v>46.4787021</v>
+        <v>49.55468440000001</v>
       </c>
       <c r="N53">
-        <v>116.5212979</v>
+        <v>113.4453156</v>
       </c>
       <c r="O53">
-        <v>29.130324475</v>
+        <v>28.3613289</v>
       </c>
       <c r="P53">
-        <v>87.390973425</v>
+        <v>85.0839867</v>
       </c>
       <c r="Q53">
-        <v>153.390973425</v>
+        <v>151.0839867</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1288553913031448</v>
+        <v>0.1303427729525564</v>
       </c>
       <c r="T53">
-        <v>1.664734022556232</v>
+        <v>1.694546594593413</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.506982609998484</v>
+        <v>3.289295491911154</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08756353101722707</v>
+        <v>0.0874696702959132</v>
       </c>
       <c r="C54">
-        <v>777.0758500835757</v>
+        <v>763.8233153563374</v>
       </c>
       <c r="D54">
-        <v>1399.159850083576</v>
+        <v>1400.774315356337</v>
       </c>
       <c r="E54">
-        <v>629.0840000000001</v>
+        <v>643.951</v>
       </c>
       <c r="F54">
-        <v>773.0840000000001</v>
+        <v>787.951</v>
       </c>
       <c r="G54">
         <v>151</v>
@@ -5703,28 +5703,28 @@
         <v>163</v>
       </c>
       <c r="M54">
-        <v>49.55468440000001</v>
+        <v>50.50765910000001</v>
       </c>
       <c r="N54">
-        <v>113.4453156</v>
+        <v>112.4923409</v>
       </c>
       <c r="O54">
-        <v>28.3613289</v>
+        <v>28.123085225</v>
       </c>
       <c r="P54">
-        <v>85.0839867</v>
+        <v>84.36925567499999</v>
       </c>
       <c r="Q54">
-        <v>151.0839867</v>
+        <v>150.369255675</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1303427729525564</v>
+        <v>0.1318934474381132</v>
       </c>
       <c r="T54">
-        <v>1.694546594593413</v>
+        <v>1.725627786717284</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.289295491911154</v>
+        <v>3.227233312818491</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0874696702959132</v>
+        <v>0.08737580957459934</v>
       </c>
       <c r="C55">
-        <v>763.8233153563374</v>
+        <v>750.5745107378237</v>
       </c>
       <c r="D55">
-        <v>1400.774315356337</v>
+        <v>1402.392510737824</v>
       </c>
       <c r="E55">
-        <v>643.951</v>
+        <v>658.8180000000001</v>
       </c>
       <c r="F55">
-        <v>787.951</v>
+        <v>802.8180000000001</v>
       </c>
       <c r="G55">
         <v>151</v>
@@ -5785,28 +5785,28 @@
         <v>163</v>
       </c>
       <c r="M55">
-        <v>50.50765910000001</v>
+        <v>51.46063380000001</v>
       </c>
       <c r="N55">
-        <v>112.4923409</v>
+        <v>111.5393662</v>
       </c>
       <c r="O55">
-        <v>28.123085225</v>
+        <v>27.88484155</v>
       </c>
       <c r="P55">
-        <v>84.36925567499999</v>
+        <v>83.65452464999998</v>
       </c>
       <c r="Q55">
-        <v>150.369255675</v>
+        <v>149.65452465</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1318934474381132</v>
+        <v>0.1335115425534768</v>
       </c>
       <c r="T55">
-        <v>1.725627786717284</v>
+        <v>1.758060335020453</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.227233312818491</v>
+        <v>3.167469732951481</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08737580957459934</v>
+        <v>0.08728194885328547</v>
       </c>
       <c r="C56">
-        <v>750.5745107378237</v>
+        <v>737.3294491702187</v>
       </c>
       <c r="D56">
-        <v>1402.392510737824</v>
+        <v>1404.014449170219</v>
       </c>
       <c r="E56">
-        <v>658.8180000000001</v>
+        <v>673.6850000000001</v>
       </c>
       <c r="F56">
-        <v>802.8180000000001</v>
+        <v>817.6850000000001</v>
       </c>
       <c r="G56">
         <v>151</v>
@@ -5867,28 +5867,28 @@
         <v>163</v>
       </c>
       <c r="M56">
-        <v>51.46063380000001</v>
+        <v>52.41360850000001</v>
       </c>
       <c r="N56">
-        <v>111.5393662</v>
+        <v>110.5863915</v>
       </c>
       <c r="O56">
-        <v>27.88484155</v>
+        <v>27.646597875</v>
       </c>
       <c r="P56">
-        <v>83.65452464999998</v>
+        <v>82.93979362499999</v>
       </c>
       <c r="Q56">
-        <v>149.65452465</v>
+        <v>148.939793625</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1335115425534768</v>
+        <v>0.135201553007301</v>
       </c>
       <c r="T56">
-        <v>1.758060335020453</v>
+        <v>1.791934329914874</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.167469732951481</v>
+        <v>3.109879374170545</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08728194885328547</v>
+        <v>0.08718808813197158</v>
       </c>
       <c r="C57">
-        <v>737.3294491702187</v>
+        <v>724.0881436556467</v>
       </c>
       <c r="D57">
-        <v>1404.014449170219</v>
+        <v>1405.640143655647</v>
       </c>
       <c r="E57">
-        <v>673.6850000000001</v>
+        <v>688.5520000000001</v>
       </c>
       <c r="F57">
-        <v>817.6850000000001</v>
+        <v>832.5520000000001</v>
       </c>
       <c r="G57">
         <v>151</v>
@@ -5949,28 +5949,28 @@
         <v>163</v>
       </c>
       <c r="M57">
-        <v>52.41360850000001</v>
+        <v>53.36658320000002</v>
       </c>
       <c r="N57">
-        <v>110.5863915</v>
+        <v>109.6334168</v>
       </c>
       <c r="O57">
-        <v>27.646597875</v>
+        <v>27.4083542</v>
       </c>
       <c r="P57">
-        <v>82.93979362499999</v>
+        <v>82.2250626</v>
       </c>
       <c r="Q57">
-        <v>148.939793625</v>
+        <v>148.2250626</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.135201553007301</v>
+        <v>0.1369683821181172</v>
       </c>
       <c r="T57">
-        <v>1.791934329914874</v>
+        <v>1.82734805184995</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.109879374170545</v>
+        <v>3.0543458139175</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08718808813197158</v>
+        <v>0.08709422741065771</v>
       </c>
       <c r="C58">
-        <v>724.0881436556467</v>
+        <v>710.8506072565233</v>
       </c>
       <c r="D58">
-        <v>1405.640143655647</v>
+        <v>1407.269607256523</v>
       </c>
       <c r="E58">
-        <v>688.5520000000001</v>
+        <v>703.4190000000001</v>
       </c>
       <c r="F58">
-        <v>832.5520000000001</v>
+        <v>847.4190000000001</v>
       </c>
       <c r="G58">
         <v>151</v>
@@ -6031,28 +6031,28 @@
         <v>163</v>
       </c>
       <c r="M58">
-        <v>53.36658320000002</v>
+        <v>54.31955790000001</v>
       </c>
       <c r="N58">
-        <v>109.6334168</v>
+        <v>108.6804421</v>
       </c>
       <c r="O58">
-        <v>27.4083542</v>
+        <v>27.170110525</v>
       </c>
       <c r="P58">
-        <v>82.2250626</v>
+        <v>81.510331575</v>
       </c>
       <c r="Q58">
-        <v>148.2250626</v>
+        <v>147.510331575</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1369683821181172</v>
+        <v>0.138817389327111</v>
       </c>
       <c r="T58">
-        <v>1.82734805184995</v>
+        <v>1.864408923642473</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.0543458139175</v>
+        <v>3.000760799638245</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08709422741065771</v>
+        <v>0.09039336668934383</v>
       </c>
       <c r="C59">
-        <v>710.8506072565233</v>
+        <v>640.8876487348108</v>
       </c>
       <c r="D59">
-        <v>1407.269607256523</v>
+        <v>1352.173648734811</v>
       </c>
       <c r="E59">
-        <v>703.4190000000001</v>
+        <v>718.2860000000002</v>
       </c>
       <c r="F59">
-        <v>847.4190000000001</v>
+        <v>862.2860000000002</v>
       </c>
       <c r="G59">
         <v>151</v>
@@ -6113,45 +6113,45 @@
         <v>163</v>
       </c>
       <c r="M59">
-        <v>54.31955790000001</v>
+        <v>61.99836340000002</v>
       </c>
       <c r="N59">
-        <v>108.6804421</v>
+        <v>101.0016366</v>
       </c>
       <c r="O59">
-        <v>27.170110525</v>
+        <v>25.25040915</v>
       </c>
       <c r="P59">
-        <v>81.510331575</v>
+        <v>75.75122744999999</v>
       </c>
       <c r="Q59">
-        <v>147.510331575</v>
+        <v>141.75122745</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.138817389327111</v>
+        <v>0.1407544444984377</v>
       </c>
       <c r="T59">
-        <v>1.864408923642473</v>
+        <v>1.903234598853686</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.000760799638245</v>
+        <v>2.62910165786731</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09039336668934383</v>
+        <v>0.09035800596802997</v>
       </c>
       <c r="C60">
-        <v>640.887648734811</v>
+        <v>626.5882948207334</v>
       </c>
       <c r="D60">
-        <v>1352.173648734811</v>
+        <v>1352.741294820733</v>
       </c>
       <c r="E60">
-        <v>718.2859999999999</v>
+        <v>733.153</v>
       </c>
       <c r="F60">
-        <v>862.2859999999999</v>
+        <v>877.153</v>
       </c>
       <c r="G60">
         <v>151</v>
@@ -6195,28 +6195,28 @@
         <v>163</v>
       </c>
       <c r="M60">
-        <v>61.9983634</v>
+        <v>63.0673007</v>
       </c>
       <c r="N60">
-        <v>101.0016366</v>
+        <v>99.9326993</v>
       </c>
       <c r="O60">
-        <v>25.25040915</v>
+        <v>24.983174825</v>
       </c>
       <c r="P60">
-        <v>75.75122745</v>
+        <v>74.949524475</v>
       </c>
       <c r="Q60">
-        <v>141.75122745</v>
+        <v>140.949524475</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1407544444984377</v>
+        <v>0.1427859901659267</v>
       </c>
       <c r="T60">
-        <v>1.903234598853686</v>
+        <v>1.943954209441056</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.62910165786731</v>
+        <v>2.584540612818712</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09035800596802997</v>
+        <v>0.0903226452467161</v>
       </c>
       <c r="C61">
-        <v>626.5882948207334</v>
+        <v>612.2894177054836</v>
       </c>
       <c r="D61">
-        <v>1352.741294820733</v>
+        <v>1353.309417705484</v>
       </c>
       <c r="E61">
-        <v>733.153</v>
+        <v>748.02</v>
       </c>
       <c r="F61">
-        <v>877.153</v>
+        <v>892.02</v>
       </c>
       <c r="G61">
         <v>151</v>
@@ -6277,28 +6277,28 @@
         <v>163</v>
       </c>
       <c r="M61">
-        <v>63.0673007</v>
+        <v>64.13623800000001</v>
       </c>
       <c r="N61">
-        <v>99.9326993</v>
+        <v>98.86376199999999</v>
       </c>
       <c r="O61">
-        <v>24.983174825</v>
+        <v>24.7159405</v>
       </c>
       <c r="P61">
-        <v>74.949524475</v>
+        <v>74.14782149999999</v>
       </c>
       <c r="Q61">
-        <v>140.949524475</v>
+        <v>140.1478215</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1427859901659267</v>
+        <v>0.1449191131167902</v>
       </c>
       <c r="T61">
-        <v>1.943954209441056</v>
+        <v>1.986709800557795</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.584540612818712</v>
+        <v>2.5414649359384</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0903226452467161</v>
+        <v>0.09207153452540223</v>
       </c>
       <c r="C62">
-        <v>612.2894177054836</v>
+        <v>569.8841076164287</v>
       </c>
       <c r="D62">
-        <v>1353.309417705484</v>
+        <v>1325.771107616429</v>
       </c>
       <c r="E62">
-        <v>748.02</v>
+        <v>762.8870000000001</v>
       </c>
       <c r="F62">
-        <v>892.02</v>
+        <v>906.8870000000001</v>
       </c>
       <c r="G62">
         <v>151</v>
@@ -6359,45 +6359,45 @@
         <v>163</v>
       </c>
       <c r="M62">
-        <v>64.13623800000001</v>
+        <v>68.74203460000001</v>
       </c>
       <c r="N62">
-        <v>98.86376199999999</v>
+        <v>94.25796539999999</v>
       </c>
       <c r="O62">
-        <v>24.7159405</v>
+        <v>23.56449135</v>
       </c>
       <c r="P62">
-        <v>74.14782149999999</v>
+        <v>70.69347404999999</v>
       </c>
       <c r="Q62">
-        <v>140.1478215</v>
+        <v>136.69347405</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1449191131167902</v>
+        <v>0.1471616269882109</v>
       </c>
       <c r="T62">
-        <v>1.986709800557795</v>
+        <v>2.031657986090777</v>
       </c>
       <c r="U62">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.5414649359384</v>
+        <v>2.371183817128392</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09207153452540223</v>
+        <v>0.09206542380408836</v>
       </c>
       <c r="C63">
-        <v>569.8841076164287</v>
+        <v>555.1113768060835</v>
       </c>
       <c r="D63">
-        <v>1325.771107616429</v>
+        <v>1325.865376806084</v>
       </c>
       <c r="E63">
-        <v>762.8870000000001</v>
+        <v>777.754</v>
       </c>
       <c r="F63">
-        <v>906.8870000000001</v>
+        <v>921.754</v>
       </c>
       <c r="G63">
         <v>151</v>
@@ -6441,28 +6441,28 @@
         <v>163</v>
       </c>
       <c r="M63">
-        <v>68.74203460000001</v>
+        <v>69.86895320000001</v>
       </c>
       <c r="N63">
-        <v>94.25796539999999</v>
+        <v>93.13104679999999</v>
       </c>
       <c r="O63">
-        <v>23.56449135</v>
+        <v>23.2827617</v>
       </c>
       <c r="P63">
-        <v>70.69347404999999</v>
+        <v>69.8482851</v>
       </c>
       <c r="Q63">
-        <v>136.69347405</v>
+        <v>135.8482851</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1471616269882109</v>
+        <v>0.1495221679054957</v>
       </c>
       <c r="T63">
-        <v>2.031657986090777</v>
+        <v>2.078971865599179</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.371183817128392</v>
+        <v>2.332938916852128</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09206542380408836</v>
+        <v>0.09205931308277449</v>
       </c>
       <c r="C64">
-        <v>555.1113768060835</v>
+        <v>540.3386594027464</v>
       </c>
       <c r="D64">
-        <v>1325.865376806084</v>
+        <v>1325.959659402746</v>
       </c>
       <c r="E64">
-        <v>777.754</v>
+        <v>792.621</v>
       </c>
       <c r="F64">
-        <v>921.754</v>
+        <v>936.621</v>
       </c>
       <c r="G64">
         <v>151</v>
@@ -6523,28 +6523,28 @@
         <v>163</v>
       </c>
       <c r="M64">
-        <v>69.86895320000001</v>
+        <v>70.9958718</v>
       </c>
       <c r="N64">
-        <v>93.13104679999999</v>
+        <v>92.0041282</v>
       </c>
       <c r="O64">
-        <v>23.2827617</v>
+        <v>23.00103205</v>
       </c>
       <c r="P64">
-        <v>69.8482851</v>
+        <v>69.00309615</v>
       </c>
       <c r="Q64">
-        <v>135.8482851</v>
+        <v>135.00309615</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1495221679054957</v>
+        <v>0.1520103056291202</v>
       </c>
       <c r="T64">
-        <v>2.078971865599179</v>
+        <v>2.128843252108035</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.332938916852128</v>
+        <v>2.295908140394157</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09205931308277449</v>
+        <v>0.09205320236146063</v>
       </c>
       <c r="C65">
-        <v>540.3386594027464</v>
+        <v>525.5659554092774</v>
       </c>
       <c r="D65">
-        <v>1325.959659402746</v>
+        <v>1326.053955409277</v>
       </c>
       <c r="E65">
-        <v>792.621</v>
+        <v>807.4880000000001</v>
       </c>
       <c r="F65">
-        <v>936.621</v>
+        <v>951.4880000000001</v>
       </c>
       <c r="G65">
         <v>151</v>
@@ -6605,28 +6605,28 @@
         <v>163</v>
       </c>
       <c r="M65">
-        <v>70.9958718</v>
+        <v>72.12279040000001</v>
       </c>
       <c r="N65">
-        <v>92.0041282</v>
+        <v>90.87720959999999</v>
       </c>
       <c r="O65">
-        <v>23.00103205</v>
+        <v>22.7193024</v>
       </c>
       <c r="P65">
-        <v>69.00309615</v>
+        <v>68.15790719999998</v>
       </c>
       <c r="Q65">
-        <v>135.00309615</v>
+        <v>134.1579072</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1520103056291202</v>
+        <v>0.1546366732262795</v>
       </c>
       <c r="T65">
-        <v>2.128843252108035</v>
+        <v>2.181485271200716</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.295908140394157</v>
+        <v>2.260034575700498</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09205320236146063</v>
+        <v>0.09204709164014674</v>
       </c>
       <c r="C66">
-        <v>525.5659554092774</v>
+        <v>510.7932648285389</v>
       </c>
       <c r="D66">
-        <v>1326.053955409277</v>
+        <v>1326.148264828539</v>
       </c>
       <c r="E66">
-        <v>807.4880000000001</v>
+        <v>822.355</v>
       </c>
       <c r="F66">
-        <v>951.4880000000001</v>
+        <v>966.355</v>
       </c>
       <c r="G66">
         <v>151</v>
@@ -6687,28 +6687,28 @@
         <v>163</v>
       </c>
       <c r="M66">
-        <v>72.12279040000001</v>
+        <v>73.24970900000001</v>
       </c>
       <c r="N66">
-        <v>90.87720959999999</v>
+        <v>89.75029099999999</v>
       </c>
       <c r="O66">
-        <v>22.7193024</v>
+        <v>22.43757275</v>
       </c>
       <c r="P66">
-        <v>68.15790719999998</v>
+        <v>67.31271824999999</v>
       </c>
       <c r="Q66">
-        <v>134.1579072</v>
+        <v>133.31271825</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1546366732262795</v>
+        <v>0.1574131189718478</v>
       </c>
       <c r="T66">
-        <v>2.181485271200716</v>
+        <v>2.237135405670122</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.260034575700498</v>
+        <v>2.225264812997414</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09204709164014674</v>
+        <v>0.09204098091883287</v>
       </c>
       <c r="C67">
-        <v>510.7932648285389</v>
+        <v>496.0205876633914</v>
       </c>
       <c r="D67">
-        <v>1326.148264828539</v>
+        <v>1326.242587663392</v>
       </c>
       <c r="E67">
-        <v>822.355</v>
+        <v>837.2220000000001</v>
       </c>
       <c r="F67">
-        <v>966.355</v>
+        <v>981.2220000000001</v>
       </c>
       <c r="G67">
         <v>151</v>
@@ -6769,28 +6769,28 @@
         <v>163</v>
       </c>
       <c r="M67">
-        <v>73.24970900000001</v>
+        <v>74.37662760000001</v>
       </c>
       <c r="N67">
-        <v>89.75029099999999</v>
+        <v>88.62337239999999</v>
       </c>
       <c r="O67">
-        <v>22.43757275</v>
+        <v>22.1558431</v>
       </c>
       <c r="P67">
-        <v>67.31271824999999</v>
+        <v>66.4675293</v>
       </c>
       <c r="Q67">
-        <v>133.31271825</v>
+        <v>132.4675293</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1574131189718478</v>
+        <v>0.1603528850553908</v>
       </c>
       <c r="T67">
-        <v>2.237135405670122</v>
+        <v>2.296059077461258</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.225264812997414</v>
+        <v>2.19154867946715</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09204098091883287</v>
+        <v>0.09203487019751901</v>
       </c>
       <c r="C68">
-        <v>496.0205876633914</v>
+        <v>481.2479239166984</v>
       </c>
       <c r="D68">
-        <v>1326.242587663392</v>
+        <v>1326.336923916698</v>
       </c>
       <c r="E68">
-        <v>837.2220000000001</v>
+        <v>852.0890000000001</v>
       </c>
       <c r="F68">
-        <v>981.2220000000001</v>
+        <v>996.0890000000001</v>
       </c>
       <c r="G68">
         <v>151</v>
@@ -6851,28 +6851,28 @@
         <v>163</v>
       </c>
       <c r="M68">
-        <v>74.37662760000001</v>
+        <v>75.50354620000002</v>
       </c>
       <c r="N68">
-        <v>88.62337239999999</v>
+        <v>87.49645379999998</v>
       </c>
       <c r="O68">
-        <v>22.1558431</v>
+        <v>21.87411345</v>
       </c>
       <c r="P68">
-        <v>66.4675293</v>
+        <v>65.62234034999999</v>
       </c>
       <c r="Q68">
-        <v>132.4675293</v>
+        <v>131.62234035</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1603528850553908</v>
+        <v>0.1634708187803606</v>
       </c>
       <c r="T68">
-        <v>2.296059077461258</v>
+        <v>2.358553880876099</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.19154867946715</v>
+        <v>2.158838997684058</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09203487019751901</v>
+        <v>0.09202875947620512</v>
       </c>
       <c r="C69">
-        <v>481.2479239166984</v>
+        <v>466.4752735913237</v>
       </c>
       <c r="D69">
-        <v>1326.336923916698</v>
+        <v>1326.431273591324</v>
       </c>
       <c r="E69">
-        <v>852.0890000000001</v>
+        <v>866.9560000000001</v>
       </c>
       <c r="F69">
-        <v>996.0890000000001</v>
+        <v>1010.956</v>
       </c>
       <c r="G69">
         <v>151</v>
@@ -6933,28 +6933,28 @@
         <v>163</v>
       </c>
       <c r="M69">
-        <v>75.50354620000002</v>
+        <v>76.63046480000001</v>
       </c>
       <c r="N69">
-        <v>87.49645379999998</v>
+        <v>86.36953519999999</v>
       </c>
       <c r="O69">
-        <v>21.87411345</v>
+        <v>21.5923838</v>
       </c>
       <c r="P69">
-        <v>65.62234034999999</v>
+        <v>64.77715139999999</v>
       </c>
       <c r="Q69">
-        <v>131.62234035</v>
+        <v>130.7771514</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1634708187803606</v>
+        <v>0.166783623363141</v>
       </c>
       <c r="T69">
-        <v>2.358553880876099</v>
+        <v>2.424954609504367</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.158838997684058</v>
+        <v>2.127091365365175</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09202875947620512</v>
+        <v>0.09202264875489126</v>
       </c>
       <c r="C70">
-        <v>466.4752735913237</v>
+        <v>451.7026366901309</v>
       </c>
       <c r="D70">
-        <v>1326.431273591324</v>
+        <v>1326.525636690131</v>
       </c>
       <c r="E70">
-        <v>866.9560000000001</v>
+        <v>881.8230000000001</v>
       </c>
       <c r="F70">
-        <v>1010.956</v>
+        <v>1025.823</v>
       </c>
       <c r="G70">
         <v>151</v>
@@ -7015,28 +7015,28 @@
         <v>163</v>
       </c>
       <c r="M70">
-        <v>76.63046480000001</v>
+        <v>77.75738340000001</v>
       </c>
       <c r="N70">
-        <v>86.36953519999999</v>
+        <v>85.24261659999999</v>
       </c>
       <c r="O70">
-        <v>21.5923838</v>
+        <v>21.31065415</v>
       </c>
       <c r="P70">
-        <v>64.77715139999999</v>
+        <v>63.93196244999999</v>
       </c>
       <c r="Q70">
-        <v>130.7771514</v>
+        <v>129.93196245</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.166783623363141</v>
+        <v>0.1703101572738428</v>
       </c>
       <c r="T70">
-        <v>2.424954609504367</v>
+        <v>2.495639256108654</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.127091365365175</v>
+        <v>2.096263954272926</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09202264875489126</v>
+        <v>0.0920165380335774</v>
       </c>
       <c r="C71">
-        <v>451.7026366901309</v>
+        <v>436.930013215986</v>
       </c>
       <c r="D71">
-        <v>1326.525636690131</v>
+        <v>1326.620013215986</v>
       </c>
       <c r="E71">
-        <v>881.8230000000001</v>
+        <v>896.6900000000001</v>
       </c>
       <c r="F71">
-        <v>1025.823</v>
+        <v>1040.69</v>
       </c>
       <c r="G71">
         <v>151</v>
@@ -7097,28 +7097,28 @@
         <v>163</v>
       </c>
       <c r="M71">
-        <v>77.75738340000001</v>
+        <v>78.88430200000001</v>
       </c>
       <c r="N71">
-        <v>85.24261659999999</v>
+        <v>84.11569799999999</v>
       </c>
       <c r="O71">
-        <v>21.31065415</v>
+        <v>21.0289245</v>
       </c>
       <c r="P71">
-        <v>63.93196244999999</v>
+        <v>63.08677349999999</v>
       </c>
       <c r="Q71">
-        <v>129.93196245</v>
+        <v>129.0867735</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1703101572738428</v>
+        <v>0.174071793445258</v>
       </c>
       <c r="T71">
-        <v>2.495639256108654</v>
+        <v>2.571036212486558</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.096263954272926</v>
+        <v>2.066317326354741</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0920165380335774</v>
+        <v>0.09201042731226353</v>
       </c>
       <c r="C72">
-        <v>436.930013215986</v>
+        <v>422.1574031717544</v>
       </c>
       <c r="D72">
-        <v>1326.620013215986</v>
+        <v>1326.714403171755</v>
       </c>
       <c r="E72">
-        <v>896.6900000000001</v>
+        <v>911.5570000000002</v>
       </c>
       <c r="F72">
-        <v>1040.69</v>
+        <v>1055.557</v>
       </c>
       <c r="G72">
         <v>151</v>
@@ -7179,28 +7179,28 @@
         <v>163</v>
       </c>
       <c r="M72">
-        <v>78.88430200000001</v>
+        <v>80.01122060000003</v>
       </c>
       <c r="N72">
-        <v>84.11569799999999</v>
+        <v>82.98877939999997</v>
       </c>
       <c r="O72">
-        <v>21.0289245</v>
+        <v>20.74719484999999</v>
       </c>
       <c r="P72">
-        <v>63.08677349999999</v>
+        <v>62.24158454999998</v>
       </c>
       <c r="Q72">
-        <v>129.0867735</v>
+        <v>128.24158455</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.174071793445258</v>
+        <v>0.1780928528009087</v>
       </c>
       <c r="T72">
-        <v>2.571036212486558</v>
+        <v>2.651632958959492</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.066317326354741</v>
+        <v>2.037214265420167</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09201042731226353</v>
+        <v>0.09200431659094965</v>
       </c>
       <c r="C73">
-        <v>422.1574031717546</v>
+        <v>407.384806560304</v>
       </c>
       <c r="D73">
-        <v>1326.714403171755</v>
+        <v>1326.808806560304</v>
       </c>
       <c r="E73">
-        <v>911.557</v>
+        <v>926.424</v>
       </c>
       <c r="F73">
-        <v>1055.557</v>
+        <v>1070.424</v>
       </c>
       <c r="G73">
         <v>151</v>
@@ -7261,28 +7261,28 @@
         <v>163</v>
       </c>
       <c r="M73">
-        <v>80.0112206</v>
+        <v>81.13813920000001</v>
       </c>
       <c r="N73">
-        <v>82.9887794</v>
+        <v>81.86186079999999</v>
       </c>
       <c r="O73">
-        <v>20.74719485</v>
+        <v>20.4654652</v>
       </c>
       <c r="P73">
-        <v>62.24158455</v>
+        <v>61.39639559999999</v>
       </c>
       <c r="Q73">
-        <v>128.24158455</v>
+        <v>127.3963956</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1780928528009087</v>
+        <v>0.182401130681963</v>
       </c>
       <c r="T73">
-        <v>2.651632958959491</v>
+        <v>2.737986615894776</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.037214265420168</v>
+        <v>2.008919622844887</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09200431659094965</v>
+        <v>0.09977270586963578</v>
       </c>
       <c r="C74">
-        <v>407.384806560304</v>
+        <v>282.4531439762936</v>
       </c>
       <c r="D74">
-        <v>1326.808806560304</v>
+        <v>1216.744143976294</v>
       </c>
       <c r="E74">
-        <v>926.424</v>
+        <v>941.2909999999999</v>
       </c>
       <c r="F74">
-        <v>1070.424</v>
+        <v>1085.291</v>
       </c>
       <c r="G74">
         <v>151</v>
@@ -7343,45 +7343,45 @@
         <v>163</v>
       </c>
       <c r="M74">
-        <v>81.13813920000001</v>
+        <v>97.67618999999999</v>
       </c>
       <c r="N74">
-        <v>81.86186079999999</v>
+        <v>65.32381000000001</v>
       </c>
       <c r="O74">
-        <v>20.4654652</v>
+        <v>16.3309525</v>
       </c>
       <c r="P74">
-        <v>61.39639559999999</v>
+        <v>48.99285750000001</v>
       </c>
       <c r="Q74">
-        <v>127.3963956</v>
+        <v>114.9928575</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.182401130681963</v>
+        <v>0.1870285402579103</v>
       </c>
       <c r="T74">
-        <v>2.737986615894776</v>
+        <v>2.830736840010453</v>
       </c>
       <c r="U74">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.008919622844887</v>
+        <v>1.668779259305671</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09977270586963578</v>
+        <v>0.09987309514832191</v>
       </c>
       <c r="C75">
-        <v>282.4531439762936</v>
+        <v>266.2831876350469</v>
       </c>
       <c r="D75">
-        <v>1216.744143976294</v>
+        <v>1215.441187635047</v>
       </c>
       <c r="E75">
-        <v>941.2909999999999</v>
+        <v>956.1580000000001</v>
       </c>
       <c r="F75">
-        <v>1085.291</v>
+        <v>1100.158</v>
       </c>
       <c r="G75">
         <v>151</v>
@@ -7425,28 +7425,28 @@
         <v>163</v>
       </c>
       <c r="M75">
-        <v>97.67618999999999</v>
+        <v>99.01422000000001</v>
       </c>
       <c r="N75">
-        <v>65.32381000000001</v>
+        <v>63.98577999999999</v>
       </c>
       <c r="O75">
-        <v>16.3309525</v>
+        <v>15.996445</v>
       </c>
       <c r="P75">
-        <v>48.99285750000001</v>
+        <v>47.989335</v>
       </c>
       <c r="Q75">
-        <v>114.9928575</v>
+        <v>113.989335</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1870285402579103</v>
+        <v>0.1920119044166227</v>
       </c>
       <c r="T75">
-        <v>2.830736840010453</v>
+        <v>2.930621696750412</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.668779259305671</v>
+        <v>1.646228188233973</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09987309514832191</v>
+        <v>0.09997348442700804</v>
       </c>
       <c r="C76">
-        <v>266.2831876350469</v>
+        <v>250.1160188628962</v>
       </c>
       <c r="D76">
-        <v>1215.441187635047</v>
+        <v>1214.141018862896</v>
       </c>
       <c r="E76">
-        <v>956.1580000000001</v>
+        <v>971.0250000000001</v>
       </c>
       <c r="F76">
-        <v>1100.158</v>
+        <v>1115.025</v>
       </c>
       <c r="G76">
         <v>151</v>
@@ -7507,28 +7507,28 @@
         <v>163</v>
       </c>
       <c r="M76">
-        <v>99.01422000000001</v>
+        <v>100.35225</v>
       </c>
       <c r="N76">
-        <v>63.98577999999999</v>
+        <v>62.64775</v>
       </c>
       <c r="O76">
-        <v>15.996445</v>
+        <v>15.6619375</v>
       </c>
       <c r="P76">
-        <v>47.989335</v>
+        <v>46.9858125</v>
       </c>
       <c r="Q76">
-        <v>113.989335</v>
+        <v>112.9858125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1920119044166227</v>
+        <v>0.1973939377080322</v>
       </c>
       <c r="T76">
-        <v>2.930621696750412</v>
+        <v>3.038497342029569</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.646228188233973</v>
+        <v>1.62427847905752</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09997348442700804</v>
+        <v>0.1000738737056942</v>
       </c>
       <c r="C77">
-        <v>250.1160188628962</v>
+        <v>233.951628723735</v>
       </c>
       <c r="D77">
-        <v>1214.141018862896</v>
+        <v>1212.843628723735</v>
       </c>
       <c r="E77">
-        <v>971.0250000000001</v>
+        <v>985.8920000000001</v>
       </c>
       <c r="F77">
-        <v>1115.025</v>
+        <v>1129.892</v>
       </c>
       <c r="G77">
         <v>151</v>
@@ -7589,28 +7589,28 @@
         <v>163</v>
       </c>
       <c r="M77">
-        <v>100.35225</v>
+        <v>101.69028</v>
       </c>
       <c r="N77">
-        <v>62.64775</v>
+        <v>61.30972</v>
       </c>
       <c r="O77">
-        <v>15.6619375</v>
+        <v>15.32743</v>
       </c>
       <c r="P77">
-        <v>46.9858125</v>
+        <v>45.98229</v>
       </c>
       <c r="Q77">
-        <v>112.9858125</v>
+        <v>111.98229</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1973939377080322</v>
+        <v>0.2032244737737257</v>
       </c>
       <c r="T77">
-        <v>3.038497342029569</v>
+        <v>3.155362624415321</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.62427847905752</v>
+        <v>1.602906393806763</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1000738737056942</v>
+        <v>0.1001742629843803</v>
       </c>
       <c r="C78">
-        <v>233.951628723735</v>
+        <v>217.79000831961</v>
       </c>
       <c r="D78">
-        <v>1212.843628723735</v>
+        <v>1211.54900831961</v>
       </c>
       <c r="E78">
-        <v>985.8920000000001</v>
+        <v>1000.759</v>
       </c>
       <c r="F78">
-        <v>1129.892</v>
+        <v>1144.759</v>
       </c>
       <c r="G78">
         <v>151</v>
@@ -7671,28 +7671,28 @@
         <v>163</v>
       </c>
       <c r="M78">
-        <v>101.69028</v>
+        <v>103.02831</v>
       </c>
       <c r="N78">
-        <v>61.30972</v>
+        <v>59.97169000000001</v>
       </c>
       <c r="O78">
-        <v>15.32743</v>
+        <v>14.9929225</v>
       </c>
       <c r="P78">
-        <v>45.98229</v>
+        <v>44.9787675</v>
       </c>
       <c r="Q78">
-        <v>111.98229</v>
+        <v>110.9787675</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2032244737737257</v>
+        <v>0.2095620129755665</v>
       </c>
       <c r="T78">
-        <v>3.155362624415321</v>
+        <v>3.282390105269401</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.602906393806763</v>
+        <v>1.582089427653429</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1001742629843803</v>
+        <v>0.1002746522630664</v>
       </c>
       <c r="C79">
-        <v>217.79000831961</v>
+        <v>201.6311487905211</v>
       </c>
       <c r="D79">
-        <v>1211.54900831961</v>
+        <v>1210.257148790521</v>
       </c>
       <c r="E79">
-        <v>1000.759</v>
+        <v>1015.626</v>
       </c>
       <c r="F79">
-        <v>1144.759</v>
+        <v>1159.626</v>
       </c>
       <c r="G79">
         <v>151</v>
@@ -7753,28 +7753,28 @@
         <v>163</v>
       </c>
       <c r="M79">
-        <v>103.02831</v>
+        <v>104.36634</v>
       </c>
       <c r="N79">
-        <v>59.97169000000001</v>
+        <v>58.63366000000001</v>
       </c>
       <c r="O79">
-        <v>14.9929225</v>
+        <v>14.658415</v>
       </c>
       <c r="P79">
-        <v>44.9787675</v>
+        <v>43.975245</v>
       </c>
       <c r="Q79">
-        <v>110.9787675</v>
+        <v>109.975245</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2095620129755665</v>
+        <v>0.2164756921048474</v>
       </c>
       <c r="T79">
-        <v>3.282390105269401</v>
+        <v>3.420965538928395</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.582089427653429</v>
+        <v>1.561806229863</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1002746522630664</v>
+        <v>0.1003750415417526</v>
       </c>
       <c r="C80">
-        <v>201.6311487905211</v>
+        <v>185.4750413142146</v>
       </c>
       <c r="D80">
-        <v>1210.257148790521</v>
+        <v>1208.968041314215</v>
       </c>
       <c r="E80">
-        <v>1015.626</v>
+        <v>1030.493</v>
       </c>
       <c r="F80">
-        <v>1159.626</v>
+        <v>1174.493</v>
       </c>
       <c r="G80">
         <v>151</v>
@@ -7835,28 +7835,28 @@
         <v>163</v>
       </c>
       <c r="M80">
-        <v>104.36634</v>
+        <v>105.70437</v>
       </c>
       <c r="N80">
-        <v>58.63366000000001</v>
+        <v>57.29562999999999</v>
       </c>
       <c r="O80">
-        <v>14.658415</v>
+        <v>14.3239075</v>
       </c>
       <c r="P80">
-        <v>43.975245</v>
+        <v>42.97172249999999</v>
       </c>
       <c r="Q80">
-        <v>109.975245</v>
+        <v>108.9717225</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2164756921048474</v>
+        <v>0.2240478168654884</v>
       </c>
       <c r="T80">
-        <v>3.420965538928395</v>
+        <v>3.572738632935867</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.561806229863</v>
+        <v>1.54203653075081</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1003750415417526</v>
+        <v>0.1004754308204387</v>
       </c>
       <c r="C81">
-        <v>185.4750413142146</v>
+        <v>169.3216771059872</v>
       </c>
       <c r="D81">
-        <v>1208.968041314215</v>
+        <v>1207.681677105987</v>
       </c>
       <c r="E81">
-        <v>1030.493</v>
+        <v>1045.36</v>
       </c>
       <c r="F81">
-        <v>1174.493</v>
+        <v>1189.36</v>
       </c>
       <c r="G81">
         <v>151</v>
@@ -7917,28 +7917,28 @@
         <v>163</v>
       </c>
       <c r="M81">
-        <v>105.70437</v>
+        <v>107.0424</v>
       </c>
       <c r="N81">
-        <v>57.29562999999999</v>
+        <v>55.9576</v>
       </c>
       <c r="O81">
-        <v>14.3239075</v>
+        <v>13.9894</v>
       </c>
       <c r="P81">
-        <v>42.97172249999999</v>
+        <v>41.9682</v>
       </c>
       <c r="Q81">
-        <v>108.9717225</v>
+        <v>107.9682</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2240478168654884</v>
+        <v>0.2323771541021935</v>
       </c>
       <c r="T81">
-        <v>3.572738632935867</v>
+        <v>3.739689036344085</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.54203653075081</v>
+        <v>1.522761074116425</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1004754308204387</v>
+        <v>0.1005758200991248</v>
       </c>
       <c r="C82">
-        <v>169.3216771059872</v>
+        <v>153.1710474184833</v>
       </c>
       <c r="D82">
-        <v>1207.681677105987</v>
+        <v>1206.398047418483</v>
       </c>
       <c r="E82">
-        <v>1045.36</v>
+        <v>1060.227</v>
       </c>
       <c r="F82">
-        <v>1189.36</v>
+        <v>1204.227</v>
       </c>
       <c r="G82">
         <v>151</v>
@@ -7999,28 +7999,28 @@
         <v>163</v>
       </c>
       <c r="M82">
-        <v>107.0424</v>
+        <v>108.38043</v>
       </c>
       <c r="N82">
-        <v>55.9576</v>
+        <v>54.61957</v>
       </c>
       <c r="O82">
-        <v>13.9894</v>
+        <v>13.6548925</v>
       </c>
       <c r="P82">
-        <v>41.9682</v>
+        <v>40.96467749999999</v>
       </c>
       <c r="Q82">
-        <v>107.9682</v>
+        <v>106.9646775</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2323771541021935</v>
+        <v>0.2415832636796043</v>
       </c>
       <c r="T82">
-        <v>3.739689036344085</v>
+        <v>3.924213166426853</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.522761074116425</v>
+        <v>1.503961554682889</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1005758200991248</v>
+        <v>0.1391454207708935</v>
       </c>
       <c r="C83">
-        <v>153.1710474184833</v>
+        <v>-211.4973018129515</v>
       </c>
       <c r="D83">
-        <v>1206.398047418483</v>
+        <v>856.5966981870486</v>
       </c>
       <c r="E83">
-        <v>1060.227</v>
+        <v>1075.094</v>
       </c>
       <c r="F83">
-        <v>1204.227</v>
+        <v>1219.094</v>
       </c>
       <c r="G83">
         <v>151</v>
@@ -8081,45 +8081,45 @@
         <v>163</v>
       </c>
       <c r="M83">
-        <v>108.38043</v>
+        <v>178.9629992</v>
       </c>
       <c r="N83">
-        <v>54.61957</v>
+        <v>-15.96299920000001</v>
       </c>
       <c r="O83">
-        <v>13.6548925</v>
+        <v>-3.990749800000003</v>
       </c>
       <c r="P83">
-        <v>40.96467749999999</v>
+        <v>-11.97224940000001</v>
       </c>
       <c r="Q83">
-        <v>106.9646775</v>
+        <v>54.02775059999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2415832636796043</v>
+        <v>0.2565506672499399</v>
       </c>
       <c r="T83">
-        <v>3.924213166426853</v>
+        <v>4.224214714332676</v>
       </c>
       <c r="U83">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.25</v>
+        <v>0.2277006989274909</v>
       </c>
       <c r="W83">
-        <v>0.0675</v>
+        <v>0.1133735373974444</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.503961554682889</v>
+        <v>0.9108027957099637</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1391454207708935</v>
+        <v>0.1401554207708935</v>
       </c>
       <c r="C84">
-        <v>-211.4973018129515</v>
+        <v>-232.8193336402034</v>
       </c>
       <c r="D84">
-        <v>856.5966981870486</v>
+        <v>850.1416663597969</v>
       </c>
       <c r="E84">
-        <v>1075.094</v>
+        <v>1089.961</v>
       </c>
       <c r="F84">
-        <v>1219.094</v>
+        <v>1233.961</v>
       </c>
       <c r="G84">
         <v>151</v>
@@ -8163,37 +8163,37 @@
         <v>163</v>
       </c>
       <c r="M84">
-        <v>178.9629992</v>
+        <v>181.1454748</v>
       </c>
       <c r="N84">
-        <v>-15.96299920000001</v>
+        <v>-18.14547480000004</v>
       </c>
       <c r="O84">
-        <v>-3.990749800000003</v>
+        <v>-4.536368700000011</v>
       </c>
       <c r="P84">
-        <v>-11.97224940000001</v>
+        <v>-13.60910610000003</v>
       </c>
       <c r="Q84">
-        <v>54.02775059999999</v>
+        <v>52.39089389999997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2565506672499399</v>
+        <v>0.2689477653234658</v>
       </c>
       <c r="T84">
-        <v>4.224214714332676</v>
+        <v>4.472697932822833</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2277006989274909</v>
+        <v>0.2249573170127018</v>
       </c>
       <c r="W84">
-        <v>0.1133735373974444</v>
+        <v>0.1137762658625354</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9108027957099637</v>
+        <v>0.8998292680508073</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1401554207708935</v>
+        <v>0.1411654207708935</v>
       </c>
       <c r="C85">
-        <v>-232.8193336402034</v>
+        <v>-254.0448070933925</v>
       </c>
       <c r="D85">
-        <v>850.1416663597969</v>
+        <v>843.7831929066077</v>
       </c>
       <c r="E85">
-        <v>1089.961</v>
+        <v>1104.828</v>
       </c>
       <c r="F85">
-        <v>1233.961</v>
+        <v>1248.828</v>
       </c>
       <c r="G85">
         <v>151</v>
@@ -8245,37 +8245,37 @@
         <v>163</v>
       </c>
       <c r="M85">
-        <v>181.1454748</v>
+        <v>183.3279504</v>
       </c>
       <c r="N85">
-        <v>-18.14547480000004</v>
+        <v>-20.32795040000005</v>
       </c>
       <c r="O85">
-        <v>-4.536368700000011</v>
+        <v>-5.081987600000012</v>
       </c>
       <c r="P85">
-        <v>-13.60910610000003</v>
+        <v>-15.24596280000004</v>
       </c>
       <c r="Q85">
-        <v>52.39089389999997</v>
+        <v>50.75403719999996</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2689477653234658</v>
+        <v>0.2828945006561824</v>
       </c>
       <c r="T85">
-        <v>4.472697932822833</v>
+        <v>4.752241553624261</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2249573170127018</v>
+        <v>0.2222792537149316</v>
       </c>
       <c r="W85">
-        <v>0.1137762658625354</v>
+        <v>0.1141694055546481</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8998292680508073</v>
+        <v>0.8891170148597263</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1411654207708935</v>
+        <v>0.1421754207708935</v>
       </c>
       <c r="C86">
-        <v>-254.0448070933923</v>
+        <v>-275.1758726585367</v>
       </c>
       <c r="D86">
-        <v>843.7831929066077</v>
+        <v>837.5191273414632</v>
       </c>
       <c r="E86">
-        <v>1104.828</v>
+        <v>1119.695</v>
       </c>
       <c r="F86">
-        <v>1248.828</v>
+        <v>1263.695</v>
       </c>
       <c r="G86">
         <v>151</v>
@@ -8327,37 +8327,37 @@
         <v>163</v>
       </c>
       <c r="M86">
-        <v>183.3279504</v>
+        <v>185.510426</v>
       </c>
       <c r="N86">
-        <v>-20.32795040000002</v>
+        <v>-22.510426</v>
       </c>
       <c r="O86">
-        <v>-5.081987600000005</v>
+        <v>-5.627606499999999</v>
       </c>
       <c r="P86">
-        <v>-15.24596280000002</v>
+        <v>-16.8828195</v>
       </c>
       <c r="Q86">
-        <v>50.75403719999998</v>
+        <v>49.1171805</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2828945006561823</v>
+        <v>0.2987008006999278</v>
       </c>
       <c r="T86">
-        <v>4.752241553624258</v>
+        <v>5.069057657199209</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2222792537149316</v>
+        <v>0.2196642036712265</v>
       </c>
       <c r="W86">
-        <v>0.1141694055546481</v>
+        <v>0.114553294901064</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8891170148597264</v>
+        <v>0.8786568146849062</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1421754207708935</v>
+        <v>0.1431854207708935</v>
       </c>
       <c r="C87">
-        <v>-275.1758726585367</v>
+        <v>-296.2146174332466</v>
       </c>
       <c r="D87">
-        <v>837.5191273414632</v>
+        <v>831.3473825667535</v>
       </c>
       <c r="E87">
-        <v>1119.695</v>
+        <v>1134.562</v>
       </c>
       <c r="F87">
-        <v>1263.695</v>
+        <v>1278.562</v>
       </c>
       <c r="G87">
         <v>151</v>
@@ -8409,37 +8409,37 @@
         <v>163</v>
       </c>
       <c r="M87">
-        <v>185.510426</v>
+        <v>187.6929016</v>
       </c>
       <c r="N87">
-        <v>-22.510426</v>
+        <v>-24.69290160000003</v>
       </c>
       <c r="O87">
-        <v>-5.627606499999999</v>
+        <v>-6.173225400000007</v>
       </c>
       <c r="P87">
-        <v>-16.8828195</v>
+        <v>-18.51967620000002</v>
       </c>
       <c r="Q87">
-        <v>49.1171805</v>
+        <v>47.48032379999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2987008006999278</v>
+        <v>0.3167651436070655</v>
       </c>
       <c r="T87">
-        <v>5.069057657199209</v>
+        <v>5.431133204142009</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2196642036712265</v>
+        <v>0.2171099687448169</v>
       </c>
       <c r="W87">
-        <v>0.114553294901064</v>
+        <v>0.1149282565882609</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8786568146849062</v>
+        <v>0.8684398749792677</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1431854207708935</v>
+        <v>0.1441954207708935</v>
       </c>
       <c r="C88">
-        <v>-296.2146174332466</v>
+        <v>-317.1630674452111</v>
       </c>
       <c r="D88">
-        <v>831.3473825667535</v>
+        <v>825.2659325547889</v>
       </c>
       <c r="E88">
-        <v>1134.562</v>
+        <v>1149.429</v>
       </c>
       <c r="F88">
-        <v>1278.562</v>
+        <v>1293.429</v>
       </c>
       <c r="G88">
         <v>151</v>
@@ -8491,37 +8491,37 @@
         <v>163</v>
       </c>
       <c r="M88">
-        <v>187.6929016</v>
+        <v>189.8753772</v>
       </c>
       <c r="N88">
-        <v>-24.69290160000003</v>
+        <v>-26.87537720000003</v>
       </c>
       <c r="O88">
-        <v>-6.173225400000007</v>
+        <v>-6.718844300000008</v>
       </c>
       <c r="P88">
-        <v>-18.51967620000002</v>
+        <v>-20.15653290000002</v>
       </c>
       <c r="Q88">
-        <v>47.48032379999998</v>
+        <v>45.84346709999998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3167651436070655</v>
+        <v>0.3376086161922244</v>
       </c>
       <c r="T88">
-        <v>5.431133204142009</v>
+        <v>5.848912681383703</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2171099687448169</v>
+        <v>0.2146144518626926</v>
       </c>
       <c r="W88">
-        <v>0.1149282565882609</v>
+        <v>0.1152945984665567</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8684398749792677</v>
+        <v>0.8584578074507703</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1441954207708935</v>
+        <v>0.1452054207708935</v>
       </c>
       <c r="C89">
-        <v>-317.1630674452111</v>
+        <v>-338.0231898696619</v>
       </c>
       <c r="D89">
-        <v>825.2659325547889</v>
+        <v>819.2728101303381</v>
       </c>
       <c r="E89">
-        <v>1149.429</v>
+        <v>1164.296</v>
       </c>
       <c r="F89">
-        <v>1293.429</v>
+        <v>1308.296</v>
       </c>
       <c r="G89">
         <v>151</v>
@@ -8573,37 +8573,37 @@
         <v>163</v>
       </c>
       <c r="M89">
-        <v>189.8753772</v>
+        <v>192.0578528</v>
       </c>
       <c r="N89">
-        <v>-26.87537720000003</v>
+        <v>-29.05785280000003</v>
       </c>
       <c r="O89">
-        <v>-6.718844300000008</v>
+        <v>-7.264463200000009</v>
       </c>
       <c r="P89">
-        <v>-20.15653290000002</v>
+        <v>-21.79338960000003</v>
       </c>
       <c r="Q89">
-        <v>45.84346709999998</v>
+        <v>44.20661039999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3376086161922244</v>
+        <v>0.3619260008749098</v>
       </c>
       <c r="T89">
-        <v>5.848912681383703</v>
+        <v>6.336322071499012</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2146144518626926</v>
+        <v>0.2121756512733438</v>
       </c>
       <c r="W89">
-        <v>0.1152945984665567</v>
+        <v>0.1156526143930731</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8584578074507703</v>
+        <v>0.8487026050933751</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1452054207708935</v>
+        <v>0.1462154207708935</v>
       </c>
       <c r="C90">
-        <v>-338.0231898696619</v>
+        <v>-358.7968951509145</v>
       </c>
       <c r="D90">
-        <v>819.2728101303381</v>
+        <v>813.3661048490856</v>
       </c>
       <c r="E90">
-        <v>1164.296</v>
+        <v>1179.163</v>
       </c>
       <c r="F90">
-        <v>1308.296</v>
+        <v>1323.163</v>
       </c>
       <c r="G90">
         <v>151</v>
@@ -8655,37 +8655,37 @@
         <v>163</v>
       </c>
       <c r="M90">
-        <v>192.0578528</v>
+        <v>194.2403284</v>
       </c>
       <c r="N90">
-        <v>-29.05785280000003</v>
+        <v>-31.24032840000001</v>
       </c>
       <c r="O90">
-        <v>-7.264463200000009</v>
+        <v>-7.810082100000002</v>
       </c>
       <c r="P90">
-        <v>-21.79338960000003</v>
+        <v>-23.43024630000001</v>
       </c>
       <c r="Q90">
-        <v>44.20661039999997</v>
+        <v>42.56975369999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3619260008749098</v>
+        <v>0.3906647282271743</v>
       </c>
       <c r="T90">
-        <v>6.336322071499012</v>
+        <v>6.912351350726195</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2121756512733438</v>
+        <v>0.2097916551916209</v>
       </c>
       <c r="W90">
-        <v>0.1156526143930731</v>
+        <v>0.1160025850178701</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8487026050933751</v>
+        <v>0.8391666207664834</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1462154207708935</v>
+        <v>0.1472254207708935</v>
       </c>
       <c r="C91">
-        <v>-358.7968951509145</v>
+        <v>-379.4860390327914</v>
       </c>
       <c r="D91">
-        <v>813.3661048490856</v>
+        <v>807.5439609672086</v>
       </c>
       <c r="E91">
-        <v>1179.163</v>
+        <v>1194.03</v>
       </c>
       <c r="F91">
-        <v>1323.163</v>
+        <v>1338.03</v>
       </c>
       <c r="G91">
         <v>151</v>
@@ -8737,37 +8737,37 @@
         <v>163</v>
       </c>
       <c r="M91">
-        <v>194.2403284</v>
+        <v>196.422804</v>
       </c>
       <c r="N91">
-        <v>-31.24032840000001</v>
+        <v>-33.42280400000001</v>
       </c>
       <c r="O91">
-        <v>-7.810082100000002</v>
+        <v>-8.355701000000003</v>
       </c>
       <c r="P91">
-        <v>-23.43024630000001</v>
+        <v>-25.06710300000001</v>
       </c>
       <c r="Q91">
-        <v>42.56975369999999</v>
+        <v>40.93289699999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3906647282271743</v>
+        <v>0.4251512010498917</v>
       </c>
       <c r="T91">
-        <v>6.912351350726195</v>
+        <v>7.603586485798814</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2097916551916209</v>
+        <v>0.2074606368006028</v>
       </c>
       <c r="W91">
-        <v>0.1160025850178701</v>
+        <v>0.1163447785176715</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8391666207664834</v>
+        <v>0.8298425472024114</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1472254207708935</v>
+        <v>0.1482354207708936</v>
       </c>
       <c r="C92">
-        <v>-379.4860390327914</v>
+        <v>-400.0924245024631</v>
       </c>
       <c r="D92">
-        <v>807.5439609672086</v>
+        <v>801.804575497537</v>
       </c>
       <c r="E92">
-        <v>1194.03</v>
+        <v>1208.897</v>
       </c>
       <c r="F92">
-        <v>1338.03</v>
+        <v>1352.897</v>
       </c>
       <c r="G92">
         <v>151</v>
@@ -8819,37 +8819,37 @@
         <v>163</v>
       </c>
       <c r="M92">
-        <v>196.422804</v>
+        <v>198.6052796</v>
       </c>
       <c r="N92">
-        <v>-33.42280400000001</v>
+        <v>-35.60527960000005</v>
       </c>
       <c r="O92">
-        <v>-8.355701000000003</v>
+        <v>-8.901319900000011</v>
       </c>
       <c r="P92">
-        <v>-25.06710300000001</v>
+        <v>-26.70395970000003</v>
       </c>
       <c r="Q92">
-        <v>40.93289699999999</v>
+        <v>39.29604029999997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4251512010498917</v>
+        <v>0.4673013344998798</v>
       </c>
       <c r="T92">
-        <v>7.603586485798814</v>
+        <v>8.448429428665351</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2074606368006028</v>
+        <v>0.2051808495830137</v>
       </c>
       <c r="W92">
-        <v>0.1163447785176715</v>
+        <v>0.1166794512812136</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8298425472024114</v>
+        <v>0.820723398332055</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1482354207708936</v>
+        <v>0.1492454207708935</v>
       </c>
       <c r="C93">
-        <v>-400.0924245024631</v>
+        <v>-420.6178036519786</v>
       </c>
       <c r="D93">
-        <v>801.804575497537</v>
+        <v>796.1461963480215</v>
       </c>
       <c r="E93">
-        <v>1208.897</v>
+        <v>1223.764</v>
       </c>
       <c r="F93">
-        <v>1352.897</v>
+        <v>1367.764</v>
       </c>
       <c r="G93">
         <v>151</v>
@@ -8901,37 +8901,37 @@
         <v>163</v>
       </c>
       <c r="M93">
-        <v>198.6052796</v>
+        <v>200.7877552</v>
       </c>
       <c r="N93">
-        <v>-35.60527960000005</v>
+        <v>-37.78775520000005</v>
       </c>
       <c r="O93">
-        <v>-8.901319900000011</v>
+        <v>-9.446938800000012</v>
       </c>
       <c r="P93">
-        <v>-26.70395970000003</v>
+        <v>-28.34081640000004</v>
       </c>
       <c r="Q93">
-        <v>39.29604029999997</v>
+        <v>37.65918359999996</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4673013344998798</v>
+        <v>0.5199890013123649</v>
       </c>
       <c r="T93">
-        <v>8.448429428665351</v>
+        <v>9.504483107248523</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2051808495830137</v>
+        <v>0.2029506229571114</v>
       </c>
       <c r="W93">
-        <v>0.1166794512812136</v>
+        <v>0.1170068485498961</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.820723398332055</v>
+        <v>0.8118024918284457</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1492454207708935</v>
+        <v>0.1502554207708935</v>
       </c>
       <c r="C94">
-        <v>-420.6178036519786</v>
+        <v>-441.0638794615317</v>
       </c>
       <c r="D94">
-        <v>796.1461963480215</v>
+        <v>790.5671205384684</v>
       </c>
       <c r="E94">
-        <v>1223.764</v>
+        <v>1238.631</v>
       </c>
       <c r="F94">
-        <v>1367.764</v>
+        <v>1382.631</v>
       </c>
       <c r="G94">
         <v>151</v>
@@ -8983,37 +8983,37 @@
         <v>163</v>
       </c>
       <c r="M94">
-        <v>200.7877552</v>
+        <v>202.9702308</v>
       </c>
       <c r="N94">
-        <v>-37.78775520000005</v>
+        <v>-39.97023080000002</v>
       </c>
       <c r="O94">
-        <v>-9.446938800000012</v>
+        <v>-9.992557700000006</v>
       </c>
       <c r="P94">
-        <v>-28.34081640000004</v>
+        <v>-29.97767310000002</v>
       </c>
       <c r="Q94">
-        <v>37.65918359999996</v>
+        <v>36.02232689999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5199890013123649</v>
+        <v>0.5877302872141313</v>
       </c>
       <c r="T94">
-        <v>9.504483107248523</v>
+        <v>10.86226640828403</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2029506229571114</v>
+        <v>0.2007683581941318</v>
       </c>
       <c r="W94">
-        <v>0.1170068485498961</v>
+        <v>0.1173272050171015</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8118024918284457</v>
+        <v>0.803073432776527</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1502554207708935</v>
+        <v>0.2043675278162631</v>
       </c>
       <c r="C95">
-        <v>-441.0638794615317</v>
+        <v>-671.7247328525848</v>
       </c>
       <c r="D95">
-        <v>790.5671205384684</v>
+        <v>574.7732671474153</v>
       </c>
       <c r="E95">
-        <v>1238.631</v>
+        <v>1253.498</v>
       </c>
       <c r="F95">
-        <v>1382.631</v>
+        <v>1397.498</v>
       </c>
       <c r="G95">
         <v>151</v>
@@ -9065,45 +9065,45 @@
         <v>163</v>
       </c>
       <c r="M95">
-        <v>202.9702308</v>
+        <v>280.6175984</v>
       </c>
       <c r="N95">
-        <v>-39.97023080000002</v>
+        <v>-117.6175984</v>
       </c>
       <c r="O95">
-        <v>-9.992557700000006</v>
+        <v>-29.4043996</v>
       </c>
       <c r="P95">
-        <v>-29.97767310000002</v>
+        <v>-88.21319880000001</v>
       </c>
       <c r="Q95">
-        <v>36.02232689999998</v>
+        <v>-22.21319880000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5877302872141313</v>
+        <v>0.7170871191726451</v>
       </c>
       <c r="T95">
-        <v>10.86226640828403</v>
+        <v>13.45505076379249</v>
       </c>
       <c r="U95">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.2007683581941318</v>
+        <v>0.145215411408068</v>
       </c>
       <c r="W95">
-        <v>0.1173272050171015</v>
+        <v>0.17164074538926</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.803073432776527</v>
+        <v>0.5808616456322719</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2043675278162631</v>
+        <v>0.205917527816263</v>
       </c>
       <c r="C96">
-        <v>-671.7247328525848</v>
+        <v>-691.0508789339907</v>
       </c>
       <c r="D96">
-        <v>574.7732671474153</v>
+        <v>570.3141210660095</v>
       </c>
       <c r="E96">
-        <v>1253.498</v>
+        <v>1268.365</v>
       </c>
       <c r="F96">
-        <v>1397.498</v>
+        <v>1412.365</v>
       </c>
       <c r="G96">
         <v>151</v>
@@ -9147,37 +9147,37 @@
         <v>163</v>
       </c>
       <c r="M96">
-        <v>280.6175984</v>
+        <v>283.6028920000001</v>
       </c>
       <c r="N96">
-        <v>-117.6175984</v>
+        <v>-120.6028920000001</v>
       </c>
       <c r="O96">
-        <v>-29.4043996</v>
+        <v>-30.15072300000001</v>
       </c>
       <c r="P96">
-        <v>-88.21319880000001</v>
+        <v>-90.45216900000004</v>
       </c>
       <c r="Q96">
-        <v>-22.21319880000001</v>
+        <v>-24.45216900000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7170871191726451</v>
+        <v>0.8513445430071745</v>
       </c>
       <c r="T96">
-        <v>13.45505076379249</v>
+        <v>16.14606091655099</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.145215411408068</v>
+        <v>0.1436868281300883</v>
       </c>
       <c r="W96">
-        <v>0.17164074538926</v>
+        <v>0.1719476849114783</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5808616456322719</v>
+        <v>0.5747473125203532</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.205917527816263</v>
+        <v>0.207467527816263</v>
       </c>
       <c r="C97">
-        <v>-691.0508789339907</v>
+        <v>-710.3083686925761</v>
       </c>
       <c r="D97">
-        <v>570.3141210660095</v>
+        <v>565.9236313074241</v>
       </c>
       <c r="E97">
-        <v>1268.365</v>
+        <v>1283.232</v>
       </c>
       <c r="F97">
-        <v>1412.365</v>
+        <v>1427.232</v>
       </c>
       <c r="G97">
         <v>151</v>
@@ -9229,37 +9229,37 @@
         <v>163</v>
       </c>
       <c r="M97">
-        <v>283.6028920000001</v>
+        <v>286.5881856</v>
       </c>
       <c r="N97">
-        <v>-120.6028920000001</v>
+        <v>-123.5881856</v>
       </c>
       <c r="O97">
-        <v>-30.15072300000001</v>
+        <v>-30.89704640000001</v>
       </c>
       <c r="P97">
-        <v>-90.45216900000004</v>
+        <v>-92.69113920000002</v>
       </c>
       <c r="Q97">
-        <v>-24.45216900000004</v>
+        <v>-26.69113920000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8513445430071745</v>
+        <v>1.052730678758969</v>
       </c>
       <c r="T97">
-        <v>16.14606091655099</v>
+        <v>20.18257614568875</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1436868281300883</v>
+        <v>0.1421900903370666</v>
       </c>
       <c r="W97">
-        <v>0.1719476849114783</v>
+        <v>0.172248229860317</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5747473125203532</v>
+        <v>0.5687603613482661</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.207467527816263</v>
+        <v>0.209017527816263</v>
       </c>
       <c r="C98">
-        <v>-710.3083686925759</v>
+        <v>-729.4987756404191</v>
       </c>
       <c r="D98">
-        <v>565.9236313074241</v>
+        <v>561.6002243595808</v>
       </c>
       <c r="E98">
-        <v>1283.232</v>
+        <v>1298.099</v>
       </c>
       <c r="F98">
-        <v>1427.232</v>
+        <v>1442.099</v>
       </c>
       <c r="G98">
         <v>151</v>
@@ -9311,37 +9311,37 @@
         <v>163</v>
       </c>
       <c r="M98">
-        <v>286.5881856</v>
+        <v>289.5734792</v>
       </c>
       <c r="N98">
-        <v>-123.5881856</v>
+        <v>-126.5734792</v>
       </c>
       <c r="O98">
-        <v>-30.89704640000001</v>
+        <v>-31.6433698</v>
       </c>
       <c r="P98">
-        <v>-92.69113920000002</v>
+        <v>-94.93010940000001</v>
       </c>
       <c r="Q98">
-        <v>-26.69113920000002</v>
+        <v>-28.93010940000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.052730678758966</v>
+        <v>1.388374238345288</v>
       </c>
       <c r="T98">
-        <v>20.1825761456887</v>
+        <v>26.91010152758493</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1421900903370666</v>
+        <v>0.1407242131170968</v>
       </c>
       <c r="W98">
-        <v>0.172248229860317</v>
+        <v>0.172542578006087</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5687603613482661</v>
+        <v>0.5628968524683873</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.209017527816263</v>
+        <v>0.210567527816263</v>
       </c>
       <c r="C99">
-        <v>-729.4987756404191</v>
+        <v>-748.6236255703996</v>
       </c>
       <c r="D99">
-        <v>561.6002243595808</v>
+        <v>557.3423744296006</v>
       </c>
       <c r="E99">
-        <v>1298.099</v>
+        <v>1312.966</v>
       </c>
       <c r="F99">
-        <v>1442.099</v>
+        <v>1456.966</v>
       </c>
       <c r="G99">
         <v>151</v>
@@ -9393,37 +9393,37 @@
         <v>163</v>
       </c>
       <c r="M99">
-        <v>289.5734792</v>
+        <v>292.5587728</v>
       </c>
       <c r="N99">
-        <v>-126.5734792</v>
+        <v>-129.5587728</v>
       </c>
       <c r="O99">
-        <v>-31.6433698</v>
+        <v>-32.38969320000001</v>
       </c>
       <c r="P99">
-        <v>-94.93010940000001</v>
+        <v>-97.16907960000003</v>
       </c>
       <c r="Q99">
-        <v>-28.93010940000001</v>
+        <v>-31.16907960000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.388374238345288</v>
+        <v>2.059661357517932</v>
       </c>
       <c r="T99">
-        <v>26.91010152758493</v>
+        <v>40.36515229137739</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1407242131170968</v>
+        <v>0.1392882517587591</v>
       </c>
       <c r="W99">
-        <v>0.172542578006087</v>
+        <v>0.1728309190468412</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5628968524683873</v>
+        <v>0.5571530070350363</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.210567527816263</v>
+        <v>0.2121175278162631</v>
       </c>
       <c r="C100">
-        <v>-748.6236255703996</v>
+        <v>-767.6843983515329</v>
       </c>
       <c r="D100">
-        <v>557.3423744296006</v>
+        <v>553.1486016484672</v>
       </c>
       <c r="E100">
-        <v>1312.966</v>
+        <v>1327.833</v>
       </c>
       <c r="F100">
-        <v>1456.966</v>
+        <v>1471.833</v>
       </c>
       <c r="G100">
         <v>151</v>
@@ -9475,37 +9475,37 @@
         <v>163</v>
       </c>
       <c r="M100">
-        <v>292.5587728</v>
+        <v>295.5440664</v>
       </c>
       <c r="N100">
-        <v>-129.5587728</v>
+        <v>-132.5440664</v>
       </c>
       <c r="O100">
-        <v>-32.38969320000001</v>
+        <v>-33.1360166</v>
       </c>
       <c r="P100">
-        <v>-97.16907960000003</v>
+        <v>-99.40804980000001</v>
       </c>
       <c r="Q100">
-        <v>-31.16907960000003</v>
+        <v>-33.40804980000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.059661357517932</v>
+        <v>4.073522715035864</v>
       </c>
       <c r="T100">
-        <v>40.36515229137739</v>
+        <v>80.73030458275478</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1392882517587591</v>
+        <v>0.1378812997207918</v>
       </c>
       <c r="W100">
-        <v>0.1728309190468412</v>
+        <v>0.173113435016065</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5571530070350363</v>
+        <v>0.5515251988831673</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2121175278162631</v>
-      </c>
-      <c r="C101">
-        <v>-767.6843983515329</v>
-      </c>
-      <c r="D101">
-        <v>553.1486016484672</v>
-      </c>
-      <c r="E101">
-        <v>1327.833</v>
-      </c>
-      <c r="F101">
-        <v>1471.833</v>
-      </c>
-      <c r="G101">
-        <v>151</v>
-      </c>
-      <c r="H101">
-        <v>1342.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>229</v>
-      </c>
-      <c r="K101">
-        <v>66</v>
-      </c>
-      <c r="L101">
-        <v>163</v>
-      </c>
-      <c r="M101">
-        <v>295.5440664</v>
-      </c>
-      <c r="N101">
-        <v>-132.5440664</v>
-      </c>
-      <c r="O101">
-        <v>-33.1360166</v>
-      </c>
-      <c r="P101">
-        <v>-99.40804980000001</v>
-      </c>
-      <c r="Q101">
-        <v>-33.40804980000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.073522715035864</v>
-      </c>
-      <c r="T101">
-        <v>80.73030458275478</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1378812997207918</v>
-      </c>
-      <c r="W101">
-        <v>0.173113435016065</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5515251988831673</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
